--- a/VA_result_IAA.xlsx
+++ b/VA_result_IAA.xlsx
@@ -2144,10 +2144,10 @@
         <v>26</v>
       </c>
       <c r="B98" t="n">
-        <v>1187532.21402094</v>
+        <v>1187532.21402416</v>
       </c>
       <c r="C98" t="n">
-        <v>122.464773324138</v>
+        <v>122.46477332447</v>
       </c>
     </row>
     <row r="99">
@@ -2155,10 +2155,10 @@
         <v>101</v>
       </c>
       <c r="B99" t="n">
-        <v>1241667.905628</v>
+        <v>1241667.90563493</v>
       </c>
       <c r="C99" t="n">
-        <v>128.047539941438</v>
+        <v>128.047539942152</v>
       </c>
     </row>
     <row r="100">
@@ -2166,10 +2166,10 @@
         <v>102</v>
       </c>
       <c r="B100" t="n">
-        <v>1242448.34360839</v>
+        <v>1242448.34361726</v>
       </c>
       <c r="C100" t="n">
-        <v>128.128022945801</v>
+        <v>128.128022946716</v>
       </c>
     </row>
     <row r="101">
@@ -2177,10 +2177,10 @@
         <v>103</v>
       </c>
       <c r="B101" t="n">
-        <v>1255190.07649044</v>
+        <v>1255190.07650006</v>
       </c>
       <c r="C101" t="n">
-        <v>129.442019661623</v>
+        <v>129.442019662615</v>
       </c>
     </row>
     <row r="102">
@@ -2188,10 +2188,10 @@
         <v>104</v>
       </c>
       <c r="B102" t="n">
-        <v>1365847.53546872</v>
+        <v>1365847.53547769</v>
       </c>
       <c r="C102" t="n">
-        <v>140.853617991671</v>
+        <v>140.853617992596</v>
       </c>
     </row>
     <row r="103">
@@ -2199,10 +2199,10 @@
         <v>105</v>
       </c>
       <c r="B103" t="n">
-        <v>1325461.69887266</v>
+        <v>1325461.69888065</v>
       </c>
       <c r="C103" t="n">
-        <v>136.688811120879</v>
+        <v>136.688811121703</v>
       </c>
     </row>
     <row r="104">
@@ -2210,10 +2210,10 @@
         <v>106</v>
       </c>
       <c r="B104" t="n">
-        <v>1290985.11099089</v>
+        <v>1290985.11099933</v>
       </c>
       <c r="C104" t="n">
-        <v>133.133398080221</v>
+        <v>133.133398081092</v>
       </c>
     </row>
     <row r="105">
@@ -2221,10 +2221,10 @@
         <v>107</v>
       </c>
       <c r="B105" t="n">
-        <v>1317814.89172288</v>
+        <v>1317814.89173267</v>
       </c>
       <c r="C105" t="n">
-        <v>135.900230825376</v>
+        <v>135.900230826386</v>
       </c>
     </row>
     <row r="106">
@@ -2232,10 +2232,10 @@
         <v>108</v>
       </c>
       <c r="B106" t="n">
-        <v>1366381.1451941</v>
+        <v>1366381.14520327</v>
       </c>
       <c r="C106" t="n">
-        <v>140.908646725452</v>
+        <v>140.908646726399</v>
       </c>
     </row>
     <row r="107">
@@ -2243,10 +2243,10 @@
         <v>109</v>
       </c>
       <c r="B107" t="n">
-        <v>1379504.80515493</v>
+        <v>1379504.80516334</v>
       </c>
       <c r="C107" t="n">
-        <v>142.262029836505</v>
+        <v>142.262029837372</v>
       </c>
     </row>
     <row r="108">
@@ -2254,10 +2254,10 @@
         <v>110</v>
       </c>
       <c r="B108" t="n">
-        <v>1338673.67148896</v>
+        <v>1338673.6714972</v>
       </c>
       <c r="C108" t="n">
-        <v>138.051301512732</v>
+        <v>138.051301513582</v>
       </c>
     </row>
     <row r="109">
@@ -2265,10 +2265,10 @@
         <v>111</v>
       </c>
       <c r="B109" t="n">
-        <v>1366163.69550484</v>
+        <v>1366163.6955139</v>
       </c>
       <c r="C109" t="n">
-        <v>140.886222132174</v>
+        <v>140.886222133109</v>
       </c>
     </row>
     <row r="110">
@@ -2276,10 +2276,10 @@
         <v>112</v>
       </c>
       <c r="B110" t="n">
-        <v>1368948.61705192</v>
+        <v>1368948.61706098</v>
       </c>
       <c r="C110" t="n">
-        <v>141.173418371536</v>
+        <v>141.173418372471</v>
       </c>
     </row>
     <row r="111">
@@ -2287,10 +2287,10 @@
         <v>113</v>
       </c>
       <c r="B111" t="n">
-        <v>1403811.15812685</v>
+        <v>1403811.15813503</v>
       </c>
       <c r="C111" t="n">
-        <v>144.768633002211</v>
+        <v>144.768633003055</v>
       </c>
     </row>
     <row r="112">
@@ -2298,10 +2298,10 @@
         <v>114</v>
       </c>
       <c r="B112" t="n">
-        <v>1385404.1185527</v>
+        <v>1385404.11856099</v>
       </c>
       <c r="C112" t="n">
-        <v>142.870399082826</v>
+        <v>142.870399083681</v>
       </c>
     </row>
     <row r="113">
@@ -2309,10 +2309,10 @@
         <v>115</v>
       </c>
       <c r="B113" t="n">
-        <v>1400195.42432813</v>
+        <v>1400195.42433556</v>
       </c>
       <c r="C113" t="n">
-        <v>144.39575888997</v>
+        <v>144.395758890737</v>
       </c>
     </row>
     <row r="114">
@@ -2320,10 +2320,10 @@
         <v>116</v>
       </c>
       <c r="B114" t="n">
-        <v>1373737.90196981</v>
+        <v>1373737.90197843</v>
       </c>
       <c r="C114" t="n">
-        <v>141.667315450647</v>
+        <v>141.667315451536</v>
       </c>
     </row>
     <row r="115">
@@ -2331,10 +2331,10 @@
         <v>117</v>
       </c>
       <c r="B115" t="n">
-        <v>1427873.59357965</v>
+        <v>1427873.59359198</v>
       </c>
       <c r="C115" t="n">
-        <v>147.250082068234</v>
+        <v>147.250082069505</v>
       </c>
     </row>
     <row r="116">
@@ -2342,10 +2342,10 @@
         <v>118</v>
       </c>
       <c r="B116" t="n">
-        <v>1428654.03155971</v>
+        <v>1428654.03157398</v>
       </c>
       <c r="C116" t="n">
-        <v>147.330565072562</v>
+        <v>147.330565074034</v>
       </c>
     </row>
     <row r="117">
@@ -2353,10 +2353,10 @@
         <v>119</v>
       </c>
       <c r="B117" t="n">
-        <v>1441395.76444159</v>
+        <v>1441395.76445659</v>
       </c>
       <c r="C117" t="n">
-        <v>148.644561788367</v>
+        <v>148.644561789914</v>
       </c>
     </row>
     <row r="118">
@@ -2364,10 +2364,10 @@
         <v>120</v>
       </c>
       <c r="B118" t="n">
-        <v>1552053.22342193</v>
+        <v>1552053.2234363</v>
       </c>
       <c r="C118" t="n">
-        <v>160.056160118628</v>
+        <v>160.05616012011</v>
       </c>
     </row>
     <row r="119">
@@ -2375,10 +2375,10 @@
         <v>121</v>
       </c>
       <c r="B119" t="n">
-        <v>1511667.38682395</v>
+        <v>1511667.38683733</v>
       </c>
       <c r="C119" t="n">
-        <v>155.891353247637</v>
+        <v>155.891353249017</v>
       </c>
     </row>
     <row r="120">
@@ -2386,10 +2386,10 @@
         <v>122</v>
       </c>
       <c r="B120" t="n">
-        <v>1477190.79894388</v>
+        <v>1477190.79895772</v>
       </c>
       <c r="C120" t="n">
-        <v>152.335940207155</v>
+        <v>152.335940208583</v>
       </c>
     </row>
     <row r="121">
@@ -2397,10 +2397,10 @@
         <v>123</v>
       </c>
       <c r="B121" t="n">
-        <v>1504020.57967401</v>
+        <v>1504020.57968919</v>
       </c>
       <c r="C121" t="n">
-        <v>155.102772952118</v>
+        <v>155.102772953684</v>
       </c>
     </row>
     <row r="122">
@@ -2408,10 +2408,10 @@
         <v>124</v>
       </c>
       <c r="B122" t="n">
-        <v>1552586.83314429</v>
+        <v>1552586.83315886</v>
       </c>
       <c r="C122" t="n">
-        <v>160.111188852098</v>
+        <v>160.111188853601</v>
       </c>
     </row>
     <row r="123">
@@ -2419,10 +2419,10 @@
         <v>125</v>
       </c>
       <c r="B123" t="n">
-        <v>1565710.49310612</v>
+        <v>1565710.49311992</v>
       </c>
       <c r="C123" t="n">
-        <v>161.464571963253</v>
+        <v>161.464571964676</v>
       </c>
     </row>
     <row r="124">
@@ -2430,10 +2430,10 @@
         <v>126</v>
       </c>
       <c r="B124" t="n">
-        <v>1524879.35944301</v>
+        <v>1524879.35945664</v>
       </c>
       <c r="C124" t="n">
-        <v>157.253843639775</v>
+        <v>157.253843641181</v>
       </c>
     </row>
     <row r="125">
@@ -2441,10 +2441,10 @@
         <v>127</v>
       </c>
       <c r="B125" t="n">
-        <v>1552369.38345593</v>
+        <v>1552369.38347039</v>
       </c>
       <c r="C125" t="n">
-        <v>160.088764258912</v>
+        <v>160.088764260404</v>
       </c>
     </row>
     <row r="126">
@@ -2452,10 +2452,10 @@
         <v>128</v>
       </c>
       <c r="B126" t="n">
-        <v>1555154.30500225</v>
+        <v>1555154.30501669</v>
       </c>
       <c r="C126" t="n">
-        <v>160.375960498196</v>
+        <v>160.375960499686</v>
       </c>
     </row>
     <row r="127">
@@ -2463,10 +2463,10 @@
         <v>129</v>
       </c>
       <c r="B127" t="n">
-        <v>1590016.84607864</v>
+        <v>1590016.84609221</v>
       </c>
       <c r="C127" t="n">
-        <v>163.971175129021</v>
+        <v>163.97117513042</v>
       </c>
     </row>
     <row r="128">
@@ -2474,10 +2474,10 @@
         <v>130</v>
       </c>
       <c r="B128" t="n">
-        <v>1571609.8065043</v>
+        <v>1571609.80651798</v>
       </c>
       <c r="C128" t="n">
-        <v>162.072941209617</v>
+        <v>162.072941211027</v>
       </c>
     </row>
     <row r="129">
@@ -2485,10 +2485,10 @@
         <v>131</v>
       </c>
       <c r="B129" t="n">
-        <v>1586401.11227983</v>
+        <v>1586401.11229265</v>
       </c>
       <c r="C129" t="n">
-        <v>163.59830101677</v>
+        <v>163.598301018093</v>
       </c>
     </row>
     <row r="130">
@@ -2496,10 +2496,10 @@
         <v>132</v>
       </c>
       <c r="B130" t="n">
-        <v>1559943.58992257</v>
+        <v>1559943.58993658</v>
       </c>
       <c r="C130" t="n">
-        <v>160.869857577557</v>
+        <v>160.869857579001</v>
       </c>
     </row>
     <row r="131">
@@ -2507,10 +2507,10 @@
         <v>133</v>
       </c>
       <c r="B131" t="n">
-        <v>1614079.28153099</v>
+        <v>1614079.2815487</v>
       </c>
       <c r="C131" t="n">
-        <v>166.452624194997</v>
+        <v>166.452624196823</v>
       </c>
     </row>
     <row r="132">
@@ -2518,10 +2518,10 @@
         <v>134</v>
       </c>
       <c r="B132" t="n">
-        <v>1614859.71951183</v>
+        <v>1614859.71953148</v>
       </c>
       <c r="C132" t="n">
-        <v>166.533107199406</v>
+        <v>166.533107201433</v>
       </c>
     </row>
     <row r="133">
@@ -2529,10 +2529,10 @@
         <v>135</v>
       </c>
       <c r="B133" t="n">
-        <v>1627601.45239298</v>
+        <v>1627601.45241338</v>
       </c>
       <c r="C133" t="n">
-        <v>167.847103915136</v>
+        <v>167.847103917239</v>
       </c>
     </row>
     <row r="134">
@@ -2540,10 +2540,10 @@
         <v>136</v>
       </c>
       <c r="B134" t="n">
-        <v>1738258.91137029</v>
+        <v>1738258.91139005</v>
       </c>
       <c r="C134" t="n">
-        <v>179.258702245085</v>
+        <v>179.258702247122</v>
       </c>
     </row>
     <row r="135">
@@ -2551,10 +2551,10 @@
         <v>137</v>
       </c>
       <c r="B135" t="n">
-        <v>1697873.07477539</v>
+        <v>1697873.07479416</v>
       </c>
       <c r="C135" t="n">
-        <v>175.093895374411</v>
+        <v>175.093895376347</v>
       </c>
     </row>
     <row r="136">
@@ -2562,10 +2562,10 @@
         <v>138</v>
       </c>
       <c r="B136" t="n">
-        <v>1663396.48689493</v>
+        <v>1663396.48691416</v>
       </c>
       <c r="C136" t="n">
-        <v>171.538482333889</v>
+        <v>171.538482335872</v>
       </c>
     </row>
     <row r="137">
@@ -2573,10 +2573,10 @@
         <v>139</v>
       </c>
       <c r="B137" t="n">
-        <v>1690226.2676253</v>
+        <v>1690226.26764587</v>
       </c>
       <c r="C137" t="n">
-        <v>174.305315078876</v>
+        <v>174.305315080998</v>
       </c>
     </row>
   </sheetData>
@@ -2635,7 +2635,7 @@
         <v>75.7290780526155</v>
       </c>
       <c r="D3" t="n">
-        <v>7.65006558642753</v>
+        <v>7.65006558642751</v>
       </c>
       <c r="E3" t="n">
         <v>12.3001591883993</v>
@@ -2655,7 +2655,7 @@
         <v>84.8478299408669</v>
       </c>
       <c r="D4" t="n">
-        <v>0.283427754609611</v>
+        <v>0.283427754609589</v>
       </c>
       <c r="E4" t="n">
         <v>12.0412820580172</v>
@@ -2675,7 +2675,7 @@
         <v>83.9050534472479</v>
       </c>
       <c r="D5" t="n">
-        <v>-8.54658074203845</v>
+        <v>-8.54658074203847</v>
       </c>
       <c r="E5" t="n">
         <v>-1.11113801528692</v>
@@ -2715,7 +2715,7 @@
         <v>86.1031441923565</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.71730803519274</v>
+        <v>-6.71730803519279</v>
       </c>
       <c r="E7" t="n">
         <v>1.09417565177337</v>
@@ -2729,7 +2729,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>1148.07606554433</v>
+        <v>1148.07606554432</v>
       </c>
       <c r="C8" t="n">
         <v>73.4342682950532</v>
@@ -2775,7 +2775,7 @@
         <v>57.6988246037425</v>
       </c>
       <c r="D10" t="n">
-        <v>7.65367682471283</v>
+        <v>7.6536768247129</v>
       </c>
       <c r="E10" t="n">
         <v>2.45732709868076</v>
@@ -2835,7 +2835,7 @@
         <v>63.322090700307</v>
       </c>
       <c r="D13" t="n">
-        <v>8.13056310558748</v>
+        <v>8.13056310558751</v>
       </c>
       <c r="E13" t="n">
         <v>10.0863021385178</v>
@@ -2855,7 +2855,7 @@
         <v>59.7690663753261</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.72474618432852</v>
+        <v>-7.72474618432851</v>
       </c>
       <c r="E14" t="n">
         <v>-5.61103445209472</v>
@@ -2915,7 +2915,7 @@
         <v>71.82320650039</v>
       </c>
       <c r="D17" t="n">
-        <v>-13.7253211297906</v>
+        <v>-13.7253211297905</v>
       </c>
       <c r="E17" t="n">
         <v>-25.9964549114521</v>
@@ -2935,7 +2935,7 @@
         <v>89.855652930818</v>
       </c>
       <c r="D18" t="n">
-        <v>24.3986532160774</v>
+        <v>24.3986532160773</v>
       </c>
       <c r="E18" t="n">
         <v>25.1067131489459</v>
@@ -2955,7 +2955,7 @@
         <v>97.0813047771494</v>
       </c>
       <c r="D19" t="n">
-        <v>11.4671077004951</v>
+        <v>11.4671077004952</v>
       </c>
       <c r="E19" t="n">
         <v>8.04139930060337</v>
@@ -3092,13 +3092,13 @@
         <v>2045.82233722826</v>
       </c>
       <c r="C26" t="n">
-        <v>127.02058896825</v>
+        <v>127.020588968988</v>
       </c>
       <c r="D26" t="n">
         <v>-6.92975658296814</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.67386349817365</v>
+        <v>-4.6738634976196</v>
       </c>
       <c r="F26" t="s">
         <v>145</v>
@@ -3109,16 +3109,16 @@
         <v>104</v>
       </c>
       <c r="B27" t="n">
-        <v>2069.4779139284</v>
+        <v>2069.47791200362</v>
       </c>
       <c r="C27" t="n">
-        <v>136.644014504537</v>
+        <v>136.644014505444</v>
       </c>
       <c r="D27" t="n">
-        <v>1.15628694973555</v>
+        <v>1.15628685565219</v>
       </c>
       <c r="E27" t="n">
-        <v>7.57627217323986</v>
+        <v>7.57627217332897</v>
       </c>
       <c r="F27" t="s">
         <v>145</v>
@@ -3129,16 +3129,16 @@
         <v>108</v>
       </c>
       <c r="B28" t="n">
-        <v>2059.49867682334</v>
+        <v>2059.4986733593</v>
       </c>
       <c r="C28" t="n">
-        <v>140.527050051716</v>
+        <v>140.527050052616</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.482210369963287</v>
+        <v>-0.482210444791176</v>
       </c>
       <c r="E28" t="n">
-        <v>2.84171652981546</v>
+        <v>2.84171652979106</v>
       </c>
       <c r="F28" t="s">
         <v>146</v>
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="B29" t="n">
-        <v>2047.93882978321</v>
+        <v>2047.93882549015</v>
       </c>
       <c r="C29" t="n">
-        <v>143.302052336636</v>
+        <v>143.302052337486</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.56129422029827</v>
+        <v>-0.561294261495848</v>
       </c>
       <c r="E29" t="n">
-        <v>1.97471040906279</v>
+        <v>1.97471040901456</v>
       </c>
       <c r="F29" t="s">
         <v>146</v>
@@ -3169,16 +3169,16 @@
         <v>116</v>
       </c>
       <c r="B30" t="n">
-        <v>2042.74893527067</v>
+        <v>2042.74893080009</v>
       </c>
       <c r="C30" t="n">
-        <v>146.223131094953</v>
+        <v>146.223131096247</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.253420387223624</v>
+        <v>-0.253420396422799</v>
       </c>
       <c r="E30" t="n">
-        <v>2.03840678530876</v>
+        <v>2.03840678560709</v>
       </c>
       <c r="F30" t="s">
         <v>146</v>
@@ -3189,16 +3189,16 @@
         <v>120</v>
       </c>
       <c r="B31" t="n">
-        <v>2090.23550312276</v>
+        <v>2090.23549982467</v>
       </c>
       <c r="C31" t="n">
-        <v>155.846556631385</v>
+        <v>155.846556632848</v>
       </c>
       <c r="D31" t="n">
-        <v>2.32464044074028</v>
+        <v>2.32464050322496</v>
       </c>
       <c r="E31" t="n">
-        <v>6.58132914017755</v>
+        <v>6.58132914023479</v>
       </c>
       <c r="F31" t="s">
         <v>145</v>
@@ -3209,16 +3209,16 @@
         <v>124</v>
       </c>
       <c r="B32" t="n">
-        <v>2100.06878197084</v>
+        <v>2100.06877938685</v>
       </c>
       <c r="C32" t="n">
-        <v>159.72959217851</v>
+        <v>159.729592179965</v>
       </c>
       <c r="D32" t="n">
-        <v>0.470438801435646</v>
+        <v>0.470438836342146</v>
       </c>
       <c r="E32" t="n">
-        <v>2.49157609321407</v>
+        <v>2.49157609318573</v>
       </c>
       <c r="F32" t="s">
         <v>145</v>
@@ -3229,16 +3229,16 @@
         <v>128</v>
       </c>
       <c r="B33" t="n">
-        <v>2104.98058673563</v>
+        <v>2104.98058492865</v>
       </c>
       <c r="C33" t="n">
-        <v>162.504594463401</v>
+        <v>162.504594464807</v>
       </c>
       <c r="D33" t="n">
-        <v>0.233887804387933</v>
+        <v>0.233887841674751</v>
       </c>
       <c r="E33" t="n">
-        <v>1.73731257122978</v>
+        <v>1.73731257118248</v>
       </c>
       <c r="F33" t="s">
         <v>145</v>
@@ -3249,16 +3249,16 @@
         <v>132</v>
       </c>
       <c r="B34" t="n">
-        <v>2113.4848294964</v>
+        <v>2113.48482862483</v>
       </c>
       <c r="C34" t="n">
-        <v>165.425673221774</v>
+        <v>165.425673223624</v>
       </c>
       <c r="D34" t="n">
-        <v>0.404005757314896</v>
+        <v>0.404005802099516</v>
       </c>
       <c r="E34" t="n">
-        <v>1.79753610537501</v>
+        <v>1.79753610563322</v>
       </c>
       <c r="F34" t="s">
         <v>145</v>
@@ -3269,16 +3269,16 @@
         <v>136</v>
       </c>
       <c r="B35" t="n">
-        <v>2172.35637548252</v>
+        <v>2172.35637652387</v>
       </c>
       <c r="C35" t="n">
-        <v>175.049098758065</v>
+        <v>175.049098760085</v>
       </c>
       <c r="D35" t="n">
-        <v>2.7855201591461</v>
+        <v>2.78552025080545</v>
       </c>
       <c r="E35" t="n">
-        <v>5.81737123922119</v>
+        <v>5.81737123925836</v>
       </c>
       <c r="F35" t="s">
         <v>145</v>
@@ -3323,16 +3323,16 @@
         <v>1293.8339602424</v>
       </c>
       <c r="C2" t="n">
-        <v>1356.1717417444</v>
+        <v>1356.17174089185</v>
       </c>
       <c r="D2" t="n">
-        <v>-62.3377815019941</v>
+        <v>-62.3377806494498</v>
       </c>
       <c r="E2" t="n">
         <v>75.7290780526155</v>
       </c>
       <c r="F2" t="n">
-        <v>-112.099647763188</v>
+        <v>-112.09964341958</v>
       </c>
     </row>
     <row r="3">
@@ -3343,16 +3343,16 @@
         <v>1297.50104478429</v>
       </c>
       <c r="C3" t="n">
-        <v>1378.40257836559</v>
+        <v>1378.40257961179</v>
       </c>
       <c r="D3" t="n">
-        <v>-80.9015335812973</v>
+        <v>-80.9015348274941</v>
       </c>
       <c r="E3" t="n">
         <v>84.8478299408669</v>
       </c>
       <c r="F3" t="n">
-        <v>-174.084999126668</v>
+        <v>-174.084996009445</v>
       </c>
     </row>
     <row r="4">
@@ -3363,16 +3363,16 @@
         <v>1186.60907036301</v>
       </c>
       <c r="C4" t="n">
-        <v>1320.08221483738</v>
+        <v>1320.08221521906</v>
       </c>
       <c r="D4" t="n">
-        <v>-133.473144474371</v>
+        <v>-133.473144856046</v>
       </c>
       <c r="E4" t="n">
         <v>83.9050534472479</v>
       </c>
       <c r="F4" t="n">
-        <v>-278.189249298083</v>
+        <v>-278.189246054065</v>
       </c>
     </row>
     <row r="5">
@@ -3383,16 +3383,16 @@
         <v>1323.77516202068</v>
       </c>
       <c r="C5" t="n">
-        <v>1242.64932127001</v>
+        <v>1242.64932240075</v>
       </c>
       <c r="D5" t="n">
-        <v>81.1258407506672</v>
+        <v>81.1258396199248</v>
       </c>
       <c r="E5" t="n">
         <v>85.171221425204</v>
       </c>
       <c r="F5" t="n">
-        <v>-150.139209161164</v>
+        <v>-150.139206087434</v>
       </c>
     </row>
     <row r="6">
@@ -3403,16 +3403,16 @@
         <v>1234.85310669437</v>
       </c>
       <c r="C6" t="n">
-        <v>1355.81561100893</v>
+        <v>1355.81561154119</v>
       </c>
       <c r="D6" t="n">
-        <v>-120.962504314557</v>
+        <v>-120.962504846813</v>
       </c>
       <c r="E6" t="n">
         <v>86.1031441923565</v>
       </c>
       <c r="F6" t="n">
-        <v>-245.770844974908</v>
+        <v>-245.770842026513</v>
       </c>
     </row>
     <row r="7">
@@ -3423,16 +3423,16 @@
         <v>1148.07606554433</v>
       </c>
       <c r="C7" t="n">
-        <v>1185.09820138357</v>
+        <v>1185.09820054263</v>
       </c>
       <c r="D7" t="n">
-        <v>-37.0221358392452</v>
+        <v>-37.0221349983014</v>
       </c>
       <c r="E7" t="n">
         <v>73.4342682950532</v>
       </c>
       <c r="F7" t="n">
-        <v>-241.335560903955</v>
+        <v>-241.335556251717</v>
       </c>
     </row>
     <row r="8">
@@ -3443,16 +3443,16 @@
         <v>1175.26553381497</v>
       </c>
       <c r="C8" t="n">
-        <v>1065.53152772342</v>
+        <v>1065.53152597645</v>
       </c>
       <c r="D8" t="n">
-        <v>109.734006091554</v>
+        <v>109.734007838525</v>
       </c>
       <c r="E8" t="n">
         <v>56.3149813074573</v>
       </c>
       <c r="F8" t="n">
-        <v>-90.8920656050168</v>
+        <v>-90.8920586503998</v>
       </c>
     </row>
     <row r="9">
@@ -3463,16 +3463,16 @@
         <v>1265.21655960541</v>
       </c>
       <c r="C9" t="n">
-        <v>1200.56872016337</v>
+        <v>1200.56871983257</v>
       </c>
       <c r="D9" t="n">
-        <v>64.6478394420333</v>
+        <v>64.6478397728389</v>
       </c>
       <c r="E9" t="n">
         <v>57.6988246037425</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.9043203628221</v>
+        <v>-10.9043135943186</v>
       </c>
     </row>
     <row r="10">
@@ -3483,16 +3483,16 @@
         <v>1279.63694954878</v>
       </c>
       <c r="C10" t="n">
-        <v>1278.42257136983</v>
+        <v>1278.42257073269</v>
       </c>
       <c r="D10" t="n">
-        <v>1.21437817895205</v>
+        <v>1.2143788160909</v>
       </c>
       <c r="E10" t="n">
         <v>59.2759139170921</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.83852766374252</v>
+        <v>-7.83852110734233</v>
       </c>
     </row>
     <row r="11">
@@ -3503,16 +3503,16 @@
         <v>1309.17111810706</v>
       </c>
       <c r="C11" t="n">
-        <v>1268.33223069159</v>
+        <v>1268.33222962808</v>
       </c>
       <c r="D11" t="n">
-        <v>40.8388874154687</v>
+        <v>40.8388884789823</v>
       </c>
       <c r="E11" t="n">
         <v>57.520408506983</v>
       </c>
       <c r="F11" t="n">
-        <v>34.3347836008113</v>
+        <v>34.3347903933102</v>
       </c>
     </row>
     <row r="12">
@@ -3523,16 +3523,16 @@
         <v>1415.61410202488</v>
       </c>
       <c r="C12" t="n">
-        <v>1345.1642450497</v>
+        <v>1345.16424477097</v>
       </c>
       <c r="D12" t="n">
-        <v>70.4498569751824</v>
+        <v>70.4498572539045</v>
       </c>
       <c r="E12" t="n">
         <v>63.322090700307</v>
       </c>
       <c r="F12" t="n">
-        <v>99.0072957470188</v>
+        <v>99.0073017592472</v>
       </c>
     </row>
     <row r="13">
@@ -3543,16 +3543,16 @@
         <v>1306.2615056939</v>
       </c>
       <c r="C13" t="n">
-        <v>1373.35013311628</v>
+        <v>1373.35013141695</v>
       </c>
       <c r="D13" t="n">
-        <v>-67.0886274223887</v>
+        <v>-67.0886257230586</v>
       </c>
       <c r="E13" t="n">
         <v>59.7690663753261</v>
       </c>
       <c r="F13" t="n">
-        <v>15.2354701864931</v>
+        <v>15.2354766765689</v>
       </c>
     </row>
     <row r="14">
@@ -3563,16 +3563,16 @@
         <v>1249.76280435067</v>
       </c>
       <c r="C14" t="n">
-        <v>1519.37631732177</v>
+        <v>1519.37632042935</v>
       </c>
       <c r="D14" t="n">
-        <v>-269.613512971101</v>
+        <v>-269.613516078684</v>
       </c>
       <c r="E14" t="n">
         <v>89.7246037908952</v>
       </c>
       <c r="F14" t="n">
-        <v>-256.934632713396</v>
+        <v>-256.934630252053</v>
       </c>
     </row>
     <row r="15">
@@ -3583,16 +3583,16 @@
         <v>1309.18056330287</v>
       </c>
       <c r="C15" t="n">
-        <v>1345.87048778105</v>
+        <v>1345.87048976254</v>
       </c>
       <c r="D15" t="n">
-        <v>-36.6899244781776</v>
+        <v>-36.6899264596686</v>
       </c>
       <c r="E15" t="n">
         <v>97.0537376479071</v>
       </c>
       <c r="F15" t="n">
-        <v>-250.284565731111</v>
+        <v>-250.284564255465</v>
       </c>
     </row>
     <row r="16">
@@ -3603,16 +3603,16 @@
         <v>1129.49132682075</v>
       </c>
       <c r="C16" t="n">
-        <v>1169.74644875675</v>
+        <v>1169.74644649526</v>
       </c>
       <c r="D16" t="n">
-        <v>-40.2551219359979</v>
+        <v>-40.255119674509</v>
       </c>
       <c r="E16" t="n">
         <v>71.82320650039</v>
       </c>
       <c r="F16" t="n">
-        <v>-248.321110121123</v>
+        <v>-248.321105252213</v>
       </c>
     </row>
     <row r="17">
@@ -3623,16 +3623,16 @@
         <v>1405.07199875742</v>
       </c>
       <c r="C17" t="n">
-        <v>1301.20731985836</v>
+        <v>1301.20732283419</v>
       </c>
       <c r="D17" t="n">
-        <v>103.864678899053</v>
+        <v>103.864675923228</v>
       </c>
       <c r="E17" t="n">
         <v>89.855652930818</v>
       </c>
       <c r="F17" t="n">
-        <v>-102.568955069101</v>
+        <v>-102.568952625382</v>
       </c>
     </row>
     <row r="18">
@@ -3643,16 +3643,16 @@
         <v>1566.19311812443</v>
       </c>
       <c r="C18" t="n">
-        <v>1474.40365220941</v>
+        <v>1474.40365347804</v>
       </c>
       <c r="D18" t="n">
-        <v>91.7894659150244</v>
+        <v>91.7894646463855</v>
       </c>
       <c r="E18" t="n">
         <v>97.0813047771494</v>
       </c>
       <c r="F18" t="n">
-        <v>6.52951355258347</v>
+        <v>6.52951502452152</v>
       </c>
     </row>
     <row r="19">
@@ -3663,16 +3663,16 @@
         <v>1626.78805854904</v>
       </c>
       <c r="C19" t="n">
-        <v>1595.42884061606</v>
+        <v>1595.42884114717</v>
       </c>
       <c r="D19" t="n">
-        <v>31.3592179329771</v>
+        <v>31.3592174018666</v>
       </c>
       <c r="E19" t="n">
         <v>101.293165942097</v>
       </c>
       <c r="F19" t="n">
-        <v>36.8002441990616</v>
+        <v>36.800245104545</v>
       </c>
     </row>
     <row r="20">
@@ -3683,16 +3683,16 @@
         <v>1572.138</v>
       </c>
       <c r="C20" t="n">
-        <v>1611.28452900475</v>
+        <v>1611.28452875336</v>
       </c>
       <c r="D20" t="n">
-        <v>-39.146529004747</v>
+        <v>-39.1465287533646</v>
       </c>
       <c r="E20" t="n">
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.53938511920455</v>
+        <v>-8.53938403980283</v>
       </c>
     </row>
     <row r="21">
@@ -3703,16 +3703,16 @@
         <v>1799.159</v>
       </c>
       <c r="C21" t="n">
-        <v>1618.38651504285</v>
+        <v>1618.38651597901</v>
       </c>
       <c r="D21" t="n">
-        <v>180.772484957146</v>
+        <v>180.772484020992</v>
       </c>
       <c r="E21" t="n">
         <v>106.221897642401</v>
       </c>
       <c r="F21" t="n">
-        <v>173.685710662393</v>
+        <v>173.685710905009</v>
       </c>
     </row>
     <row r="22">
@@ -3723,16 +3723,16 @@
         <v>1837.48745054851</v>
       </c>
       <c r="C22" t="n">
-        <v>1857.58684180041</v>
+        <v>1857.58684285061</v>
       </c>
       <c r="D22" t="n">
-        <v>-20.099391251893</v>
+        <v>-20.0993923020961</v>
       </c>
       <c r="E22" t="n">
         <v>118.403515958076</v>
       </c>
       <c r="F22" t="n">
-        <v>124.309952839589</v>
+        <v>124.309951443895</v>
       </c>
     </row>
     <row r="23">
@@ -3743,16 +3743,16 @@
         <v>2009.72567286795</v>
       </c>
       <c r="C23" t="n">
-        <v>1855.26649314522</v>
+        <v>1855.26649378135</v>
       </c>
       <c r="D23" t="n">
-        <v>154.459179722736</v>
+        <v>154.459179086601</v>
       </c>
       <c r="E23" t="n">
         <v>123.782765725369</v>
       </c>
       <c r="F23" t="n">
-        <v>257.81909744158</v>
+        <v>257.819095322429</v>
       </c>
     </row>
     <row r="24">
@@ -3763,16 +3763,16 @@
         <v>2198.14869083481</v>
       </c>
       <c r="C24" t="n">
-        <v>2034.41190003616</v>
+        <v>2034.41190073681</v>
       </c>
       <c r="D24" t="n">
-        <v>163.73679079865</v>
+        <v>163.736790098004</v>
       </c>
       <c r="E24" t="n">
         <v>133.248439126468</v>
       </c>
       <c r="F24" t="n">
-        <v>378.09194267838</v>
+        <v>378.091939286187</v>
       </c>
     </row>
     <row r="25">
@@ -3783,16 +3783,16 @@
         <v>2045.82233722826</v>
       </c>
       <c r="C25" t="n">
-        <v>2089.56413745675</v>
+        <v>2089.56413571987</v>
       </c>
       <c r="D25" t="n">
-        <v>-43.7418002284924</v>
+        <v>-43.7417984916156</v>
       </c>
       <c r="E25" t="n">
-        <v>127.02058896825</v>
+        <v>127.020588968988</v>
       </c>
       <c r="F25" t="n">
-        <v>270.604349721458</v>
+        <v>270.604347161535</v>
       </c>
     </row>
   </sheetData>
@@ -3849,31 +3849,31 @@
         <v>19.0235910981994</v>
       </c>
       <c r="C2" t="n">
-        <v>-59.8548209275739</v>
+        <v>-59.8548177000365</v>
       </c>
       <c r="D2" t="n">
-        <v>339.700425033629</v>
+        <v>339.700424832775</v>
       </c>
       <c r="E2" t="n">
-        <v>1356.1717417444</v>
+        <v>1356.17174089185</v>
       </c>
       <c r="F2" t="n">
         <v>1293.8339602424</v>
       </c>
       <c r="G2" t="n">
-        <v>-62.3377815019942</v>
+        <v>-62.3377806494498</v>
       </c>
       <c r="H2" t="n">
-        <v>-16.1527924853522</v>
+        <v>-16.1527920886481</v>
       </c>
       <c r="I2" t="n">
-        <v>323.547632548277</v>
+        <v>323.547632744127</v>
       </c>
       <c r="J2" t="n">
         <v>1293.8339602424</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="3">
@@ -3884,31 +3884,31 @@
         <v>19.540739677546</v>
       </c>
       <c r="C3" t="n">
-        <v>-59.8548209275739</v>
+        <v>-59.8548177000365</v>
       </c>
       <c r="D3" t="n">
-        <v>343.423748617293</v>
+        <v>343.42374848599</v>
       </c>
       <c r="E3" t="n">
-        <v>1356.1717417444</v>
+        <v>1356.17174089185</v>
       </c>
       <c r="F3" t="n">
         <v>1293.8339602424</v>
       </c>
       <c r="G3" t="n">
-        <v>-62.3377815019942</v>
+        <v>-62.3377806494498</v>
       </c>
       <c r="H3" t="n">
-        <v>-15.9254536414108</v>
+        <v>-15.9254533181339</v>
       </c>
       <c r="I3" t="n">
-        <v>327.498294975882</v>
+        <v>327.498295167857</v>
       </c>
       <c r="J3" t="n">
         <v>1293.8339602424</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="4">
@@ -3919,31 +3919,31 @@
         <v>17.5813453888002</v>
       </c>
       <c r="C4" t="n">
-        <v>-59.8548209275739</v>
+        <v>-59.8548177000365</v>
       </c>
       <c r="D4" t="n">
-        <v>329.31666362017</v>
+        <v>329.316663225347</v>
       </c>
       <c r="E4" t="n">
-        <v>1356.1717417444</v>
+        <v>1356.17174089185</v>
       </c>
       <c r="F4" t="n">
         <v>1293.8339602424</v>
       </c>
       <c r="G4" t="n">
-        <v>-62.3377815019942</v>
+        <v>-62.3377806494498</v>
       </c>
       <c r="H4" t="n">
-        <v>-15.4707759535278</v>
+        <v>-15.4707757771054</v>
       </c>
       <c r="I4" t="n">
-        <v>313.845887666642</v>
+        <v>313.845887448242</v>
       </c>
       <c r="J4" t="n">
         <v>1293.8339602424</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="5">
@@ -3954,31 +3954,31 @@
         <v>19.5834018880699</v>
       </c>
       <c r="C5" t="n">
-        <v>-59.8548209275739</v>
+        <v>-59.8548177000365</v>
       </c>
       <c r="D5" t="n">
-        <v>343.730904473305</v>
+        <v>343.73090434774</v>
       </c>
       <c r="E5" t="n">
-        <v>1356.1717417444</v>
+        <v>1356.17174089185</v>
       </c>
       <c r="F5" t="n">
         <v>1293.8339602424</v>
       </c>
       <c r="G5" t="n">
-        <v>-62.3377815019942</v>
+        <v>-62.3377806494498</v>
       </c>
       <c r="H5" t="n">
-        <v>-14.7887594217034</v>
+        <v>-14.7887594655626</v>
       </c>
       <c r="I5" t="n">
-        <v>328.942145051602</v>
+        <v>328.942144882177</v>
       </c>
       <c r="J5" t="n">
         <v>1293.8339602424</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="6">
@@ -3989,31 +3989,31 @@
         <v>21.3315046724616</v>
       </c>
       <c r="C6" t="n">
-        <v>-112.099647763188</v>
+        <v>-112.09964341958</v>
       </c>
       <c r="D6" t="n">
-        <v>345.457975561787</v>
+        <v>345.45797607956</v>
       </c>
       <c r="E6" t="n">
-        <v>1378.38907842896</v>
+        <v>1378.38908043574</v>
       </c>
       <c r="F6" t="n">
         <v>1297.50104478429</v>
       </c>
       <c r="G6" t="n">
-        <v>-80.8880336446641</v>
+        <v>-80.8880356514439</v>
       </c>
       <c r="H6" t="n">
-        <v>-13.8794040459375</v>
+        <v>-13.8794043835056</v>
       </c>
       <c r="I6" t="n">
-        <v>331.57857151585</v>
+        <v>331.578571696054</v>
       </c>
       <c r="J6" t="n">
         <v>1297.50104478429</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="7">
@@ -4024,31 +4024,31 @@
         <v>22.1736020548486</v>
       </c>
       <c r="C7" t="n">
-        <v>-112.099647763188</v>
+        <v>-112.09964341958</v>
       </c>
       <c r="D7" t="n">
-        <v>351.52083867077</v>
+        <v>351.520839301797</v>
       </c>
       <c r="E7" t="n">
-        <v>1378.38907842896</v>
+        <v>1378.38908043574</v>
       </c>
       <c r="F7" t="n">
         <v>1297.50104478429</v>
       </c>
       <c r="G7" t="n">
-        <v>-80.8880336446641</v>
+        <v>-80.8880356514439</v>
       </c>
       <c r="H7" t="n">
-        <v>-16.0527036417226</v>
+        <v>-16.052704162425</v>
       </c>
       <c r="I7" t="n">
-        <v>335.468135029047</v>
+        <v>335.468135139372</v>
       </c>
       <c r="J7" t="n">
         <v>1297.50104478429</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="8">
@@ -4059,31 +4059,31 @@
         <v>19.5932337266586</v>
       </c>
       <c r="C8" t="n">
-        <v>-112.099647763188</v>
+        <v>-112.09964341958</v>
       </c>
       <c r="D8" t="n">
-        <v>332.942916126676</v>
+        <v>332.942916410668</v>
       </c>
       <c r="E8" t="n">
-        <v>1378.38907842896</v>
+        <v>1378.38908043574</v>
       </c>
       <c r="F8" t="n">
         <v>1297.50104478429</v>
       </c>
       <c r="G8" t="n">
-        <v>-80.8880336446641</v>
+        <v>-80.8880356514439</v>
       </c>
       <c r="H8" t="n">
-        <v>-21.3086582090585</v>
+        <v>-21.3086588023207</v>
       </c>
       <c r="I8" t="n">
-        <v>311.634257917617</v>
+        <v>311.634257608347</v>
       </c>
       <c r="J8" t="n">
         <v>1297.50104478429</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="9">
@@ -4094,31 +4094,31 @@
         <v>21.7494894868981</v>
       </c>
       <c r="C9" t="n">
-        <v>-112.099647763188</v>
+        <v>-112.09964341958</v>
       </c>
       <c r="D9" t="n">
-        <v>348.467348069725</v>
+        <v>348.467348643713</v>
       </c>
       <c r="E9" t="n">
-        <v>1378.38907842896</v>
+        <v>1378.38908043574</v>
       </c>
       <c r="F9" t="n">
         <v>1297.50104478429</v>
       </c>
       <c r="G9" t="n">
-        <v>-80.8880336446641</v>
+        <v>-80.8880356514439</v>
       </c>
       <c r="H9" t="n">
-        <v>-29.6472677479454</v>
+        <v>-29.6472683031929</v>
       </c>
       <c r="I9" t="n">
-        <v>318.82008032178</v>
+        <v>318.82008034052</v>
       </c>
       <c r="J9" t="n">
         <v>1297.50104478429</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="10">
@@ -4129,31 +4129,31 @@
         <v>21.6775413501649</v>
       </c>
       <c r="C10" t="n">
-        <v>-174.084999126668</v>
+        <v>-174.084996009445</v>
       </c>
       <c r="D10" t="n">
-        <v>335.066057248889</v>
+        <v>335.066057767433</v>
       </c>
       <c r="E10" t="n">
-        <v>1320.06821588042</v>
+        <v>1320.06821757734</v>
       </c>
       <c r="F10" t="n">
         <v>1186.60907036301</v>
       </c>
       <c r="G10" t="n">
-        <v>-133.459145517412</v>
+        <v>-133.459147214329</v>
       </c>
       <c r="H10" t="n">
-        <v>-41.0685322583832</v>
+        <v>-41.0685326650415</v>
       </c>
       <c r="I10" t="n">
-        <v>293.997524990506</v>
+        <v>293.997525102392</v>
       </c>
       <c r="J10" t="n">
         <v>1186.60907036301</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="11">
@@ -4164,31 +4164,31 @@
         <v>22.6390072732588</v>
       </c>
       <c r="C11" t="n">
-        <v>-174.084999126668</v>
+        <v>-174.084996009445</v>
       </c>
       <c r="D11" t="n">
-        <v>341.988340107845</v>
+        <v>341.988340755698</v>
       </c>
       <c r="E11" t="n">
-        <v>1320.06821588042</v>
+        <v>1320.06821757734</v>
       </c>
       <c r="F11" t="n">
         <v>1186.60907036301</v>
       </c>
       <c r="G11" t="n">
-        <v>-133.459145517412</v>
+        <v>-133.459147214329</v>
       </c>
       <c r="H11" t="n">
-        <v>-42.5555397109462</v>
+        <v>-42.5555400651973</v>
       </c>
       <c r="I11" t="n">
-        <v>299.432800396899</v>
+        <v>299.4328006905</v>
       </c>
       <c r="J11" t="n">
         <v>1186.60907036301</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="12">
@@ -4199,31 +4199,31 @@
         <v>19.3315654852518</v>
       </c>
       <c r="C12" t="n">
-        <v>-174.084999126668</v>
+        <v>-174.084996009445</v>
       </c>
       <c r="D12" t="n">
-        <v>318.175694182295</v>
+        <v>318.175694385328</v>
       </c>
       <c r="E12" t="n">
-        <v>1320.06821588042</v>
+        <v>1320.06821757734</v>
       </c>
       <c r="F12" t="n">
         <v>1186.60907036301</v>
       </c>
       <c r="G12" t="n">
-        <v>-133.459145517412</v>
+        <v>-133.459147214329</v>
       </c>
       <c r="H12" t="n">
-        <v>-34.1082901056344</v>
+        <v>-34.1082905036602</v>
       </c>
       <c r="I12" t="n">
-        <v>284.06740407666</v>
+        <v>284.067403881668</v>
       </c>
       <c r="J12" t="n">
         <v>1186.60907036301</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="13">
@@ -4234,31 +4234,31 @@
         <v>20.2569393385724</v>
       </c>
       <c r="C13" t="n">
-        <v>-174.084999126668</v>
+        <v>-174.084996009445</v>
       </c>
       <c r="D13" t="n">
-        <v>324.838124341395</v>
+        <v>324.838124668882</v>
       </c>
       <c r="E13" t="n">
-        <v>1320.06821588042</v>
+        <v>1320.06821757734</v>
       </c>
       <c r="F13" t="n">
         <v>1186.60907036301</v>
       </c>
       <c r="G13" t="n">
-        <v>-133.459145517412</v>
+        <v>-133.459147214329</v>
       </c>
       <c r="H13" t="n">
-        <v>-15.7267834424478</v>
+        <v>-15.7267839804302</v>
       </c>
       <c r="I13" t="n">
-        <v>309.111340898947</v>
+        <v>309.111340688452</v>
       </c>
       <c r="J13" t="n">
         <v>1186.60907036301</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="14">
@@ -4269,31 +4269,31 @@
         <v>21.2635057619602</v>
       </c>
       <c r="C14" t="n">
-        <v>-278.189249298083</v>
+        <v>-278.189246054065</v>
       </c>
       <c r="D14" t="n">
-        <v>310.44767225556</v>
+        <v>310.447673096006</v>
       </c>
       <c r="E14" t="n">
-        <v>1242.6344842096</v>
+        <v>1242.63448758715</v>
       </c>
       <c r="F14" t="n">
         <v>1323.77516202068</v>
       </c>
       <c r="G14" t="n">
-        <v>81.1406778110763</v>
+        <v>81.1406744335277</v>
       </c>
       <c r="H14" t="n">
-        <v>12.5889802786137</v>
+        <v>12.5889795044926</v>
       </c>
       <c r="I14" t="n">
-        <v>323.036652534173</v>
+        <v>323.036652600499</v>
       </c>
       <c r="J14" t="n">
         <v>1323.77516202068</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="15">
@@ -4304,31 +4304,31 @@
         <v>21.9922000041835</v>
       </c>
       <c r="C15" t="n">
-        <v>-278.189249298083</v>
+        <v>-278.189246054065</v>
       </c>
       <c r="D15" t="n">
-        <v>315.694064812179</v>
+        <v>315.694065750628</v>
       </c>
       <c r="E15" t="n">
-        <v>1242.6344842096</v>
+        <v>1242.63448758715</v>
       </c>
       <c r="F15" t="n">
         <v>1323.77516202068</v>
       </c>
       <c r="G15" t="n">
-        <v>81.1406778110763</v>
+        <v>81.1406744335277</v>
       </c>
       <c r="H15" t="n">
-        <v>26.9937614367004</v>
+        <v>26.9937605400174</v>
       </c>
       <c r="I15" t="n">
-        <v>342.687826248879</v>
+        <v>342.687826290645</v>
       </c>
       <c r="J15" t="n">
         <v>1323.77516202068</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="16">
@@ -4339,31 +4339,31 @@
         <v>22.3679119304002</v>
       </c>
       <c r="C16" t="n">
-        <v>-278.189249298083</v>
+        <v>-278.189246054065</v>
       </c>
       <c r="D16" t="n">
-        <v>318.39908447464</v>
+        <v>318.399085463619</v>
       </c>
       <c r="E16" t="n">
-        <v>1242.6344842096</v>
+        <v>1242.63448758715</v>
       </c>
       <c r="F16" t="n">
         <v>1323.77516202068</v>
       </c>
       <c r="G16" t="n">
-        <v>81.1406778110763</v>
+        <v>81.1406744335277</v>
       </c>
       <c r="H16" t="n">
-        <v>27.4875600318124</v>
+        <v>27.4875591261442</v>
       </c>
       <c r="I16" t="n">
-        <v>345.886644506453</v>
+        <v>345.886644589763</v>
       </c>
       <c r="J16" t="n">
         <v>1323.77516202068</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="17">
@@ -4374,31 +4374,31 @@
         <v>19.54760372866</v>
       </c>
       <c r="C17" t="n">
-        <v>-278.189249298083</v>
+        <v>-278.189246054065</v>
       </c>
       <c r="D17" t="n">
-        <v>298.093662667221</v>
+        <v>298.093663276895</v>
       </c>
       <c r="E17" t="n">
-        <v>1242.6344842096</v>
+        <v>1242.63448758715</v>
       </c>
       <c r="F17" t="n">
         <v>1323.77516202068</v>
       </c>
       <c r="G17" t="n">
-        <v>81.1406778110763</v>
+        <v>81.1406744335277</v>
       </c>
       <c r="H17" t="n">
-        <v>14.0703760639497</v>
+        <v>14.070375262873</v>
       </c>
       <c r="I17" t="n">
-        <v>312.164038731171</v>
+        <v>312.164038539768</v>
       </c>
       <c r="J17" t="n">
         <v>1323.77516202068</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="18">
@@ -4409,31 +4409,31 @@
         <v>20.1695374222423</v>
       </c>
       <c r="C18" t="n">
-        <v>-150.139209161164</v>
+        <v>-150.139206087434</v>
       </c>
       <c r="D18" t="n">
-        <v>329.18584448604</v>
+        <v>329.185844711943</v>
       </c>
       <c r="E18" t="n">
-        <v>1355.80180483036</v>
+        <v>1355.80180646358</v>
       </c>
       <c r="F18" t="n">
         <v>1234.85310669437</v>
       </c>
       <c r="G18" t="n">
-        <v>-120.948698135983</v>
+        <v>-120.948699769204</v>
       </c>
       <c r="H18" t="n">
-        <v>-13.2577904668877</v>
+        <v>-13.2577910497962</v>
       </c>
       <c r="I18" t="n">
-        <v>315.928054019152</v>
+        <v>315.928053662147</v>
       </c>
       <c r="J18" t="n">
         <v>1234.85310669437</v>
       </c>
       <c r="K18" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="19">
@@ -4444,31 +4444,31 @@
         <v>23.1070041934309</v>
       </c>
       <c r="C19" t="n">
-        <v>-150.139209161164</v>
+        <v>-150.139206087434</v>
       </c>
       <c r="D19" t="n">
-        <v>350.334774875087</v>
+        <v>350.334775496051</v>
       </c>
       <c r="E19" t="n">
-        <v>1355.80180483036</v>
+        <v>1355.80180646358</v>
       </c>
       <c r="F19" t="n">
         <v>1234.85310669437</v>
       </c>
       <c r="G19" t="n">
-        <v>-120.948698135983</v>
+        <v>-120.948699769204</v>
       </c>
       <c r="H19" t="n">
-        <v>-30.9808107060658</v>
+        <v>-30.9808111318659</v>
       </c>
       <c r="I19" t="n">
-        <v>319.353964169021</v>
+        <v>319.353964364185</v>
       </c>
       <c r="J19" t="n">
         <v>1234.85310669437</v>
       </c>
       <c r="K19" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="20">
@@ -4479,31 +4479,31 @@
         <v>21.9346280696804</v>
       </c>
       <c r="C20" t="n">
-        <v>-150.139209161164</v>
+        <v>-150.139206087434</v>
       </c>
       <c r="D20" t="n">
-        <v>341.893998191528</v>
+        <v>341.893998654819</v>
       </c>
       <c r="E20" t="n">
-        <v>1355.80180483036</v>
+        <v>1355.80180646358</v>
       </c>
       <c r="F20" t="n">
         <v>1234.85310669437</v>
       </c>
       <c r="G20" t="n">
-        <v>-120.948698135983</v>
+        <v>-120.948699769204</v>
       </c>
       <c r="H20" t="n">
-        <v>-39.0986846535847</v>
+        <v>-39.098684983336</v>
       </c>
       <c r="I20" t="n">
-        <v>302.795313537943</v>
+        <v>302.795313671483</v>
       </c>
       <c r="J20" t="n">
         <v>1234.85310669437</v>
       </c>
       <c r="K20" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="21">
@@ -4514,31 +4514,31 @@
         <v>20.8919745070029</v>
       </c>
       <c r="C21" t="n">
-        <v>-150.139209161164</v>
+        <v>-150.139206087434</v>
       </c>
       <c r="D21" t="n">
-        <v>334.387187277702</v>
+        <v>334.387187600766</v>
       </c>
       <c r="E21" t="n">
-        <v>1355.80180483036</v>
+        <v>1355.80180646358</v>
       </c>
       <c r="F21" t="n">
         <v>1234.85310669437</v>
       </c>
       <c r="G21" t="n">
-        <v>-120.948698135983</v>
+        <v>-120.948699769204</v>
       </c>
       <c r="H21" t="n">
-        <v>-37.6114123094442</v>
+        <v>-37.6114126042066</v>
       </c>
       <c r="I21" t="n">
-        <v>296.775774968258</v>
+        <v>296.775774996559</v>
       </c>
       <c r="J21" t="n">
         <v>1234.85310669437</v>
       </c>
       <c r="K21" t="n">
-        <v>0.000000000000227373675443232</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="22">
@@ -4549,31 +4549,31 @@
         <v>21.0463432330779</v>
       </c>
       <c r="C22" t="n">
-        <v>-245.770844974908</v>
+        <v>-245.770842026513</v>
       </c>
       <c r="D22" t="n">
-        <v>315.62213489396</v>
+        <v>315.622135534382</v>
       </c>
       <c r="E22" t="n">
-        <v>1185.08362531132</v>
+        <v>1185.08362642709</v>
       </c>
       <c r="F22" t="n">
         <v>1148.07606554433</v>
       </c>
       <c r="G22" t="n">
-        <v>-37.0075597669943</v>
+        <v>-37.0075608827622</v>
       </c>
       <c r="H22" t="n">
-        <v>-26.5189936736444</v>
+        <v>-26.5189939944776</v>
       </c>
       <c r="I22" t="n">
-        <v>289.103141220316</v>
+        <v>289.103141539905</v>
       </c>
       <c r="J22" t="n">
-        <v>1148.07606554433</v>
+        <v>1148.07606554432</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="23">
@@ -4584,31 +4584,31 @@
         <v>20.766927703781</v>
       </c>
       <c r="C23" t="n">
-        <v>-245.770844974908</v>
+        <v>-245.770842026513</v>
       </c>
       <c r="D23" t="n">
-        <v>313.610422068243</v>
+        <v>313.610422671087</v>
       </c>
       <c r="E23" t="n">
-        <v>1185.08362531132</v>
+        <v>1185.08362642709</v>
       </c>
       <c r="F23" t="n">
         <v>1148.07606554433</v>
       </c>
       <c r="G23" t="n">
-        <v>-37.0075597669943</v>
+        <v>-37.0075608827622</v>
       </c>
       <c r="H23" t="n">
-        <v>-15.1751847265662</v>
+        <v>-15.1751850410712</v>
       </c>
       <c r="I23" t="n">
-        <v>298.435237341677</v>
+        <v>298.435237630015</v>
       </c>
       <c r="J23" t="n">
-        <v>1148.07606554433</v>
+        <v>1148.07606554432</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="24">
@@ -4619,31 +4619,31 @@
         <v>18.2413589421869</v>
       </c>
       <c r="C24" t="n">
-        <v>-245.770844974908</v>
+        <v>-245.770842026513</v>
       </c>
       <c r="D24" t="n">
-        <v>295.427040912891</v>
+        <v>295.42704117607</v>
       </c>
       <c r="E24" t="n">
-        <v>1185.08362531132</v>
+        <v>1185.08362642709</v>
       </c>
       <c r="F24" t="n">
         <v>1148.07606554433</v>
       </c>
       <c r="G24" t="n">
-        <v>-37.0075597669943</v>
+        <v>-37.0075608827622</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.57998546820946</v>
+        <v>-3.57998574398758</v>
       </c>
       <c r="I24" t="n">
-        <v>291.847055444682</v>
+        <v>291.847055432082</v>
       </c>
       <c r="J24" t="n">
-        <v>1148.07606554433</v>
+        <v>1148.07606554432</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="25">
@@ -4654,31 +4654,31 @@
         <v>13.3796384160073</v>
       </c>
       <c r="C25" t="n">
-        <v>-245.770844974908</v>
+        <v>-245.770842026513</v>
       </c>
       <c r="D25" t="n">
-        <v>260.424027436225</v>
+        <v>260.424027045549</v>
       </c>
       <c r="E25" t="n">
-        <v>1185.08362531132</v>
+        <v>1185.08362642709</v>
       </c>
       <c r="F25" t="n">
         <v>1148.07606554433</v>
       </c>
       <c r="G25" t="n">
-        <v>-37.0075597669943</v>
+        <v>-37.0075608827622</v>
       </c>
       <c r="H25" t="n">
-        <v>8.26660410142574</v>
+        <v>8.26660389677338</v>
       </c>
       <c r="I25" t="n">
-        <v>268.690631537651</v>
+        <v>268.690630942322</v>
       </c>
       <c r="J25" t="n">
-        <v>1148.07606554433</v>
+        <v>1148.07606554432</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="26">
@@ -4689,31 +4689,31 @@
         <v>14.0182406770477</v>
       </c>
       <c r="C26" t="n">
-        <v>-241.335560903955</v>
+        <v>-241.335556251717</v>
       </c>
       <c r="D26" t="n">
-        <v>265.943630464269</v>
+        <v>265.943630498648</v>
       </c>
       <c r="E26" t="n">
-        <v>1065.51698735794</v>
+        <v>1065.51698752801</v>
       </c>
       <c r="F26" t="n">
         <v>1175.26553381497</v>
       </c>
       <c r="G26" t="n">
-        <v>109.748546457031</v>
+        <v>109.748546286965</v>
       </c>
       <c r="H26" t="n">
-        <v>20.3645839823394</v>
+        <v>20.3645838812117</v>
       </c>
       <c r="I26" t="n">
-        <v>286.308214446608</v>
+        <v>286.30821437986</v>
       </c>
       <c r="J26" t="n">
         <v>1175.26553381497</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>-0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="27">
@@ -4724,31 +4724,31 @@
         <v>13.7071095233237</v>
       </c>
       <c r="C27" t="n">
-        <v>-241.335560903955</v>
+        <v>-241.335556251717</v>
       </c>
       <c r="D27" t="n">
-        <v>263.703574108053</v>
+        <v>263.703574100588</v>
       </c>
       <c r="E27" t="n">
-        <v>1065.51698735794</v>
+        <v>1065.51698752801</v>
       </c>
       <c r="F27" t="n">
         <v>1175.26553381497</v>
       </c>
       <c r="G27" t="n">
-        <v>109.748546457031</v>
+        <v>109.748546286965</v>
       </c>
       <c r="H27" t="n">
-        <v>28.0327969874723</v>
+        <v>28.0327969511988</v>
       </c>
       <c r="I27" t="n">
-        <v>291.736371095526</v>
+        <v>291.736371051787</v>
       </c>
       <c r="J27" t="n">
         <v>1175.26553381497</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>-0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="28">
@@ -4759,31 +4759,31 @@
         <v>13.8299159840223</v>
       </c>
       <c r="C28" t="n">
-        <v>-241.335560903955</v>
+        <v>-241.335556251717</v>
       </c>
       <c r="D28" t="n">
-        <v>264.587745910136</v>
+        <v>264.587745919187</v>
       </c>
       <c r="E28" t="n">
-        <v>1065.51698735794</v>
+        <v>1065.51698752801</v>
       </c>
       <c r="F28" t="n">
         <v>1175.26553381497</v>
       </c>
       <c r="G28" t="n">
-        <v>109.748546457031</v>
+        <v>109.748546286965</v>
       </c>
       <c r="H28" t="n">
-        <v>31.2712431168242</v>
+        <v>31.2712431067346</v>
       </c>
       <c r="I28" t="n">
-        <v>295.85898902696</v>
+        <v>295.858989025922</v>
       </c>
       <c r="J28" t="n">
         <v>1175.26553381497</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>-0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="29">
@@ -4794,31 +4794,31 @@
         <v>14.7597151230636</v>
       </c>
       <c r="C29" t="n">
-        <v>-241.335560903955</v>
+        <v>-241.335556251717</v>
       </c>
       <c r="D29" t="n">
-        <v>271.282036875485</v>
+        <v>271.282037009585</v>
       </c>
       <c r="E29" t="n">
-        <v>1065.51698735794</v>
+        <v>1065.51698752801</v>
       </c>
       <c r="F29" t="n">
         <v>1175.26553381497</v>
       </c>
       <c r="G29" t="n">
-        <v>109.748546457031</v>
+        <v>109.748546286965</v>
       </c>
       <c r="H29" t="n">
-        <v>30.0799223703953</v>
+        <v>30.0799223478193</v>
       </c>
       <c r="I29" t="n">
-        <v>301.36195924588</v>
+        <v>301.361959357404</v>
       </c>
       <c r="J29" t="n">
         <v>1175.26553381497</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>-0.000000000000909494701772928</v>
       </c>
     </row>
     <row r="30">
@@ -4829,31 +4829,31 @@
         <v>12.9810429170346</v>
       </c>
       <c r="C30" t="n">
-        <v>-90.8920656050168</v>
+        <v>-90.8920586503998</v>
       </c>
       <c r="D30" t="n">
-        <v>289.74488055105</v>
+        <v>289.744880416898</v>
       </c>
       <c r="E30" t="n">
-        <v>1200.55539096086</v>
+        <v>1200.55539120089</v>
       </c>
       <c r="F30" t="n">
         <v>1265.21655960541</v>
       </c>
       <c r="G30" t="n">
-        <v>64.661168644544</v>
+        <v>64.6611684045192</v>
       </c>
       <c r="H30" t="n">
-        <v>24.4588347481855</v>
+        <v>24.4588346744528</v>
       </c>
       <c r="I30" t="n">
-        <v>314.203715299236</v>
+        <v>314.203715091351</v>
       </c>
       <c r="J30" t="n">
         <v>1265.21655960541</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="31">
@@ -4864,31 +4864,31 @@
         <v>13.8683680277628</v>
       </c>
       <c r="C31" t="n">
-        <v>-90.8920656050168</v>
+        <v>-90.8920586503998</v>
       </c>
       <c r="D31" t="n">
-        <v>296.133370519109</v>
+        <v>296.133370504293</v>
       </c>
       <c r="E31" t="n">
-        <v>1200.55539096086</v>
+        <v>1200.55539120089</v>
       </c>
       <c r="F31" t="n">
         <v>1265.21655960541</v>
       </c>
       <c r="G31" t="n">
-        <v>64.661168644544</v>
+        <v>64.6611684045192</v>
       </c>
       <c r="H31" t="n">
-        <v>18.8929826644818</v>
+        <v>18.892982575777</v>
       </c>
       <c r="I31" t="n">
-        <v>315.026353183591</v>
+        <v>315.02635308007</v>
       </c>
       <c r="J31" t="n">
         <v>1265.21655960541</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="32">
@@ -4899,31 +4899,31 @@
         <v>17.0680954411519</v>
       </c>
       <c r="C32" t="n">
-        <v>-90.8920656050168</v>
+        <v>-90.8920586503998</v>
       </c>
       <c r="D32" t="n">
-        <v>319.170503396125</v>
+        <v>319.170503811642</v>
       </c>
       <c r="E32" t="n">
-        <v>1200.55539096086</v>
+        <v>1200.55539120089</v>
       </c>
       <c r="F32" t="n">
         <v>1265.21655960541</v>
       </c>
       <c r="G32" t="n">
-        <v>64.661168644544</v>
+        <v>64.6611684045192</v>
       </c>
       <c r="H32" t="n">
-        <v>13.3823661192841</v>
+        <v>13.3823660517917</v>
       </c>
       <c r="I32" t="n">
-        <v>332.552869515409</v>
+        <v>332.552869863434</v>
       </c>
       <c r="J32" t="n">
         <v>1265.21655960541</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="33">
@@ -4934,31 +4934,31 @@
         <v>13.7813182177931</v>
       </c>
       <c r="C33" t="n">
-        <v>-90.8920656050168</v>
+        <v>-90.8920586503998</v>
       </c>
       <c r="D33" t="n">
-        <v>295.506636494579</v>
+        <v>295.506636468056</v>
       </c>
       <c r="E33" t="n">
-        <v>1200.55539096086</v>
+        <v>1200.55539120089</v>
       </c>
       <c r="F33" t="n">
         <v>1265.21655960541</v>
       </c>
       <c r="G33" t="n">
-        <v>64.661168644544</v>
+        <v>64.6611684045192</v>
       </c>
       <c r="H33" t="n">
-        <v>7.92698511259241</v>
+        <v>7.92698510249714</v>
       </c>
       <c r="I33" t="n">
-        <v>303.433621607172</v>
+        <v>303.433621570553</v>
       </c>
       <c r="J33" t="n">
         <v>1265.21655960541</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="34">
@@ -4969,31 +4969,31 @@
         <v>15.7211460315555</v>
       </c>
       <c r="C34" t="n">
-        <v>-10.9043203628221</v>
+        <v>-10.9043135943186</v>
       </c>
       <c r="D34" t="n">
-        <v>326.097822881092</v>
+        <v>326.097822806907</v>
       </c>
       <c r="E34" t="n">
-        <v>1278.40988611802</v>
+        <v>1278.40988533595</v>
       </c>
       <c r="F34" t="n">
         <v>1279.63694954878</v>
       </c>
       <c r="G34" t="n">
-        <v>1.22706343075834</v>
+        <v>1.22706421282828</v>
       </c>
       <c r="H34" t="n">
-        <v>2.52683964440678</v>
+        <v>2.52683972789318</v>
       </c>
       <c r="I34" t="n">
-        <v>328.624662525499</v>
+        <v>328.6246625348</v>
       </c>
       <c r="J34" t="n">
         <v>1279.63694954878</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="35">
@@ -5004,31 +5004,31 @@
         <v>15.2880061963509</v>
       </c>
       <c r="C35" t="n">
-        <v>-10.9043203628221</v>
+        <v>-10.9043135943186</v>
       </c>
       <c r="D35" t="n">
-        <v>322.979338507646</v>
+        <v>322.979338375209</v>
       </c>
       <c r="E35" t="n">
-        <v>1278.40988611802</v>
+        <v>1278.40988533595</v>
       </c>
       <c r="F35" t="n">
         <v>1279.63694954878</v>
       </c>
       <c r="G35" t="n">
-        <v>1.22706343075834</v>
+        <v>1.22706421282828</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.521248057554387</v>
+        <v>-0.521247891822899</v>
       </c>
       <c r="I35" t="n">
-        <v>322.458090450092</v>
+        <v>322.458090483386</v>
       </c>
       <c r="J35" t="n">
         <v>1279.63694954878</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="36">
@@ -5039,31 +5039,31 @@
         <v>14.5093569170751</v>
       </c>
       <c r="C36" t="n">
-        <v>-10.9043203628221</v>
+        <v>-10.9043135943186</v>
       </c>
       <c r="D36" t="n">
-        <v>317.373283805546</v>
+        <v>317.373283568388</v>
       </c>
       <c r="E36" t="n">
-        <v>1278.40988611802</v>
+        <v>1278.40988533595</v>
       </c>
       <c r="F36" t="n">
         <v>1279.63694954878</v>
       </c>
       <c r="G36" t="n">
-        <v>1.22706343075834</v>
+        <v>1.22706421282828</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2172779932911</v>
+        <v>-1.21727775665108</v>
       </c>
       <c r="I36" t="n">
-        <v>316.156005812255</v>
+        <v>316.156005811736</v>
       </c>
       <c r="J36" t="n">
         <v>1279.63694954878</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="37">
@@ -5074,31 +5074,31 @@
         <v>13.7574047721106</v>
       </c>
       <c r="C37" t="n">
-        <v>-10.9043203628221</v>
+        <v>-10.9043135943186</v>
       </c>
       <c r="D37" t="n">
-        <v>311.959440923738</v>
+        <v>311.959440585449</v>
       </c>
       <c r="E37" t="n">
-        <v>1278.40988611802</v>
+        <v>1278.40988533595</v>
       </c>
       <c r="F37" t="n">
         <v>1279.63694954878</v>
       </c>
       <c r="G37" t="n">
-        <v>1.22706343075834</v>
+        <v>1.22706421282828</v>
       </c>
       <c r="H37" t="n">
-        <v>0.438749837196647</v>
+        <v>0.438750133408653</v>
       </c>
       <c r="I37" t="n">
-        <v>312.398190760935</v>
+        <v>312.398190718858</v>
       </c>
       <c r="J37" t="n">
         <v>1279.63694954878</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.000000000000227373675443232</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="38">
@@ -5109,31 +5109,31 @@
         <v>13.8684629626477</v>
       </c>
       <c r="C38" t="n">
-        <v>-7.83852766374252</v>
+        <v>-7.83852110734233</v>
       </c>
       <c r="D38" t="n">
-        <v>313.39623517905</v>
+        <v>313.39623480127</v>
       </c>
       <c r="E38" t="n">
-        <v>1268.31957012131</v>
+        <v>1268.31956888543</v>
       </c>
       <c r="F38" t="n">
         <v>1309.17111810706</v>
       </c>
       <c r="G38" t="n">
-        <v>40.8515479857522</v>
+        <v>40.8515492216325</v>
       </c>
       <c r="H38" t="n">
-        <v>4.44683543390886</v>
+        <v>4.44683577835628</v>
       </c>
       <c r="I38" t="n">
-        <v>317.843070612959</v>
+        <v>317.843070579626</v>
       </c>
       <c r="J38" t="n">
         <v>1309.17111810706</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="39">
@@ -5144,31 +5144,31 @@
         <v>14.1451731996518</v>
       </c>
       <c r="C39" t="n">
-        <v>-7.83852766374252</v>
+        <v>-7.83852110734233</v>
       </c>
       <c r="D39" t="n">
-        <v>315.388470664992</v>
+        <v>315.388470324426</v>
       </c>
       <c r="E39" t="n">
-        <v>1268.31957012131</v>
+        <v>1268.31956888543</v>
       </c>
       <c r="F39" t="n">
         <v>1309.17111810706</v>
       </c>
       <c r="G39" t="n">
-        <v>40.8515479857522</v>
+        <v>40.8515492216325</v>
       </c>
       <c r="H39" t="n">
-        <v>8.35649029760539</v>
+        <v>8.356490647156</v>
       </c>
       <c r="I39" t="n">
-        <v>323.744960962597</v>
+        <v>323.744960971582</v>
       </c>
       <c r="J39" t="n">
         <v>1309.17111810706</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="40">
@@ -5179,31 +5179,31 @@
         <v>14.2458871681251</v>
       </c>
       <c r="C40" t="n">
-        <v>-7.83852766374252</v>
+        <v>-7.83852110734233</v>
       </c>
       <c r="D40" t="n">
-        <v>316.113582768161</v>
+        <v>316.11358244114</v>
       </c>
       <c r="E40" t="n">
-        <v>1268.31957012131</v>
+        <v>1268.31956888543</v>
       </c>
       <c r="F40" t="n">
         <v>1309.17111810706</v>
       </c>
       <c r="G40" t="n">
-        <v>40.8515479857522</v>
+        <v>40.8515492216325</v>
       </c>
       <c r="H40" t="n">
-        <v>12.1677144282862</v>
+        <v>12.1677147398078</v>
       </c>
       <c r="I40" t="n">
-        <v>328.281297196447</v>
+        <v>328.281297180948</v>
       </c>
       <c r="J40" t="n">
         <v>1309.17111810706</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="41">
@@ -5214,31 +5214,31 @@
         <v>15.2608851765584</v>
       </c>
       <c r="C41" t="n">
-        <v>-7.83852766374252</v>
+        <v>-7.83852110734233</v>
       </c>
       <c r="D41" t="n">
-        <v>323.421281509104</v>
+        <v>323.421281318591</v>
       </c>
       <c r="E41" t="n">
-        <v>1268.31957012131</v>
+        <v>1268.31956888543</v>
       </c>
       <c r="F41" t="n">
         <v>1309.17111810706</v>
       </c>
       <c r="G41" t="n">
-        <v>40.8515479857522</v>
+        <v>40.8515492216325</v>
       </c>
       <c r="H41" t="n">
-        <v>15.8805078259514</v>
+        <v>15.8805080563118</v>
       </c>
       <c r="I41" t="n">
-        <v>339.301789335056</v>
+        <v>339.301789374903</v>
       </c>
       <c r="J41" t="n">
         <v>1309.17111810706</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000682121026329696</v>
       </c>
     </row>
     <row r="42">
@@ -5249,31 +5249,31 @@
         <v>16.5093813838776</v>
       </c>
       <c r="C42" t="n">
-        <v>34.3347836008113</v>
+        <v>34.3347903933102</v>
       </c>
       <c r="D42" t="n">
-        <v>341.175571803641</v>
+        <v>341.175571687824</v>
       </c>
       <c r="E42" t="n">
-        <v>1345.15192400059</v>
+        <v>1345.15192317212</v>
       </c>
       <c r="F42" t="n">
         <v>1415.61410202488</v>
       </c>
       <c r="G42" t="n">
-        <v>70.4621780242876</v>
+        <v>70.4621788527572</v>
       </c>
       <c r="H42" t="n">
-        <v>19.4948704906008</v>
+        <v>19.4948705966678</v>
       </c>
       <c r="I42" t="n">
-        <v>360.670442294242</v>
+        <v>360.670442284491</v>
       </c>
       <c r="J42" t="n">
         <v>1415.61410202488</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="43">
@@ -5284,31 +5284,31 @@
         <v>15.1700534476325</v>
       </c>
       <c r="C43" t="n">
-        <v>34.3347836008113</v>
+        <v>34.3347903933102</v>
       </c>
       <c r="D43" t="n">
-        <v>331.532789264081</v>
+        <v>331.532788968137</v>
       </c>
       <c r="E43" t="n">
-        <v>1345.15192400059</v>
+        <v>1345.15192317212</v>
       </c>
       <c r="F43" t="n">
         <v>1415.61410202488</v>
       </c>
       <c r="G43" t="n">
-        <v>70.4621780242876</v>
+        <v>70.4621788527572</v>
       </c>
       <c r="H43" t="n">
-        <v>20.188885162649</v>
+        <v>20.1888852594188</v>
       </c>
       <c r="I43" t="n">
-        <v>351.72167442673</v>
+        <v>351.721674227556</v>
       </c>
       <c r="J43" t="n">
         <v>1415.61410202488</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="44">
@@ -5319,31 +5319,31 @@
         <v>16.9821700879659</v>
       </c>
       <c r="C44" t="n">
-        <v>34.3347836008113</v>
+        <v>34.3347903933102</v>
       </c>
       <c r="D44" t="n">
-        <v>344.579516825101</v>
+        <v>344.579516772869</v>
       </c>
       <c r="E44" t="n">
-        <v>1345.15192400059</v>
+        <v>1345.15192317212</v>
       </c>
       <c r="F44" t="n">
         <v>1415.61410202488</v>
       </c>
       <c r="G44" t="n">
-        <v>70.4621780242876</v>
+        <v>70.4621788527572</v>
       </c>
       <c r="H44" t="n">
-        <v>17.9625518420959</v>
+        <v>17.9625520445647</v>
       </c>
       <c r="I44" t="n">
-        <v>362.542068667197</v>
+        <v>362.542068817434</v>
       </c>
       <c r="J44" t="n">
         <v>1415.61410202488</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="45">
@@ -5354,31 +5354,31 @@
         <v>14.660485780831</v>
       </c>
       <c r="C45" t="n">
-        <v>34.3347836008113</v>
+        <v>34.3347903933102</v>
       </c>
       <c r="D45" t="n">
-        <v>327.864046107769</v>
+        <v>327.864045743293</v>
       </c>
       <c r="E45" t="n">
-        <v>1345.15192400059</v>
+        <v>1345.15192317212</v>
       </c>
       <c r="F45" t="n">
         <v>1415.61410202488</v>
       </c>
       <c r="G45" t="n">
-        <v>70.4621780242876</v>
+        <v>70.4621788527572</v>
       </c>
       <c r="H45" t="n">
-        <v>12.8158705289415</v>
+        <v>12.8158709521055</v>
       </c>
       <c r="I45" t="n">
-        <v>340.67991663671</v>
+        <v>340.679916695398</v>
       </c>
       <c r="J45" t="n">
         <v>1415.61410202488</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="46">
@@ -5389,31 +5389,31 @@
         <v>13.9855209946961</v>
       </c>
       <c r="C46" t="n">
-        <v>99.0072957470188</v>
+        <v>99.0073017592472</v>
       </c>
       <c r="D46" t="n">
-        <v>336.446285319404</v>
+        <v>336.446284483782</v>
       </c>
       <c r="E46" t="n">
-        <v>1373.33833272081</v>
+        <v>1373.33832989301</v>
       </c>
       <c r="F46" t="n">
         <v>1306.2615056939</v>
       </c>
       <c r="G46" t="n">
-        <v>-67.0768270269116</v>
+        <v>-67.0768241991136</v>
       </c>
       <c r="H46" t="n">
-        <v>4.74884122318587</v>
+        <v>4.74884198204118</v>
       </c>
       <c r="I46" t="n">
-        <v>341.19512654259</v>
+        <v>341.195126465823</v>
       </c>
       <c r="J46" t="n">
         <v>1306.2615056939</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="47">
@@ -5424,31 +5424,31 @@
         <v>13.2548173622158</v>
       </c>
       <c r="C47" t="n">
-        <v>99.0072957470188</v>
+        <v>99.0073017592472</v>
       </c>
       <c r="D47" t="n">
-        <v>331.18542572095</v>
+        <v>331.185424787055</v>
       </c>
       <c r="E47" t="n">
-        <v>1373.33833272081</v>
+        <v>1373.33832989301</v>
       </c>
       <c r="F47" t="n">
         <v>1306.2615056939</v>
       </c>
       <c r="G47" t="n">
-        <v>-67.0768270269116</v>
+        <v>-67.0768241991136</v>
       </c>
       <c r="H47" t="n">
-        <v>-7.08518969108193</v>
+        <v>-7.08518881871241</v>
       </c>
       <c r="I47" t="n">
-        <v>324.100236029868</v>
+        <v>324.100235968342</v>
       </c>
       <c r="J47" t="n">
         <v>1306.2615056939</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="48">
@@ -5459,31 +5459,31 @@
         <v>15.4351622089786</v>
       </c>
       <c r="C48" t="n">
-        <v>99.0072957470188</v>
+        <v>99.0073017592472</v>
       </c>
       <c r="D48" t="n">
-        <v>346.883292277461</v>
+        <v>346.883291636801</v>
       </c>
       <c r="E48" t="n">
-        <v>1373.33833272081</v>
+        <v>1373.33832989301</v>
       </c>
       <c r="F48" t="n">
         <v>1306.2615056939</v>
       </c>
       <c r="G48" t="n">
-        <v>-67.0768270269116</v>
+        <v>-67.0768241991136</v>
       </c>
       <c r="H48" t="n">
-        <v>-22.6862222138619</v>
+        <v>-22.6862214501553</v>
       </c>
       <c r="I48" t="n">
-        <v>324.197070063599</v>
+        <v>324.197070186645</v>
       </c>
       <c r="J48" t="n">
         <v>1306.2615056939</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="49">
@@ -5494,31 +5494,31 @@
         <v>17.0935658094356</v>
       </c>
       <c r="C49" t="n">
-        <v>99.0072957470188</v>
+        <v>99.0073017592472</v>
       </c>
       <c r="D49" t="n">
-        <v>358.823329402993</v>
+        <v>358.823328985373</v>
       </c>
       <c r="E49" t="n">
-        <v>1373.33833272081</v>
+        <v>1373.33832989301</v>
       </c>
       <c r="F49" t="n">
         <v>1306.2615056939</v>
       </c>
       <c r="G49" t="n">
-        <v>-67.0768270269116</v>
+        <v>-67.0768241991136</v>
       </c>
       <c r="H49" t="n">
-        <v>-42.054256345154</v>
+        <v>-42.0542559122875</v>
       </c>
       <c r="I49" t="n">
-        <v>316.769073057839</v>
+        <v>316.769073073085</v>
       </c>
       <c r="J49" t="n">
         <v>1306.2615056939</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="50">
@@ -5529,31 +5529,31 @@
         <v>22.375630978957</v>
       </c>
       <c r="C50" t="n">
-        <v>15.2354701864931</v>
+        <v>15.2354766765689</v>
       </c>
       <c r="D50" t="n">
-        <v>379.441232547122</v>
+        <v>379.441233221841</v>
       </c>
       <c r="E50" t="n">
-        <v>1519.36384251141</v>
+        <v>1519.36384524015</v>
       </c>
       <c r="F50" t="n">
         <v>1249.76280435067</v>
       </c>
       <c r="G50" t="n">
-        <v>-269.601038160738</v>
+        <v>-269.601040889478</v>
       </c>
       <c r="H50" t="n">
-        <v>-65.1892920849583</v>
+        <v>-65.189292205109</v>
       </c>
       <c r="I50" t="n">
-        <v>314.251940462164</v>
+        <v>314.251941016732</v>
       </c>
       <c r="J50" t="n">
         <v>1249.76280435067</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="51">
@@ -5564,31 +5564,31 @@
         <v>21.944785948544</v>
       </c>
       <c r="C51" t="n">
-        <v>15.2354701864931</v>
+        <v>15.2354766765689</v>
       </c>
       <c r="D51" t="n">
-        <v>376.339270119482</v>
+        <v>376.339270736256</v>
       </c>
       <c r="E51" t="n">
-        <v>1519.36384251141</v>
+        <v>1519.36384524015</v>
       </c>
       <c r="F51" t="n">
         <v>1249.76280435067</v>
       </c>
       <c r="G51" t="n">
-        <v>-269.601038160738</v>
+        <v>-269.601040889478</v>
       </c>
       <c r="H51" t="n">
-        <v>-75.3276933629706</v>
+        <v>-75.3276939291419</v>
       </c>
       <c r="I51" t="n">
-        <v>301.011576756511</v>
+        <v>301.011576807114</v>
       </c>
       <c r="J51" t="n">
         <v>1249.76280435067</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="52">
@@ -5599,31 +5599,31 @@
         <v>22.6041959806654</v>
       </c>
       <c r="C52" t="n">
-        <v>15.2354701864931</v>
+        <v>15.2354766765689</v>
       </c>
       <c r="D52" t="n">
-        <v>381.086835948637</v>
+        <v>381.086836654095</v>
       </c>
       <c r="E52" t="n">
-        <v>1519.36384251141</v>
+        <v>1519.36384524015</v>
       </c>
       <c r="F52" t="n">
         <v>1249.76280435067</v>
       </c>
       <c r="G52" t="n">
-        <v>-269.601038160738</v>
+        <v>-269.601040889478</v>
       </c>
       <c r="H52" t="n">
-        <v>-72.4694601791908</v>
+        <v>-72.4694610843862</v>
       </c>
       <c r="I52" t="n">
-        <v>308.617375769446</v>
+        <v>308.617375569709</v>
       </c>
       <c r="J52" t="n">
         <v>1249.76280435067</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="53">
@@ -5634,31 +5634,31 @@
         <v>22.7999908827289</v>
       </c>
       <c r="C53" t="n">
-        <v>15.2354701864931</v>
+        <v>15.2354766765689</v>
       </c>
       <c r="D53" t="n">
-        <v>382.496503896164</v>
+        <v>382.496504627955</v>
       </c>
       <c r="E53" t="n">
-        <v>1519.36384251141</v>
+        <v>1519.36384524015</v>
       </c>
       <c r="F53" t="n">
         <v>1249.76280435067</v>
       </c>
       <c r="G53" t="n">
-        <v>-269.601038160738</v>
+        <v>-269.601040889478</v>
       </c>
       <c r="H53" t="n">
-        <v>-56.6145925336189</v>
+        <v>-56.6145936708418</v>
       </c>
       <c r="I53" t="n">
-        <v>325.881911362545</v>
+        <v>325.881910957113</v>
       </c>
       <c r="J53" t="n">
         <v>1249.76280435067</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="54">
@@ -5669,31 +5669,31 @@
         <v>24.9287895301318</v>
       </c>
       <c r="C54" t="n">
-        <v>-256.934632713396</v>
+        <v>-256.934630252053</v>
       </c>
       <c r="D54" t="n">
-        <v>341.254324226395</v>
+        <v>341.254325325403</v>
       </c>
       <c r="E54" t="n">
-        <v>1345.85582183342</v>
+        <v>1345.85582587152</v>
       </c>
       <c r="F54" t="n">
         <v>1309.18056330287</v>
       </c>
       <c r="G54" t="n">
-        <v>-36.6752585305469</v>
+        <v>-36.6752625686433</v>
       </c>
       <c r="H54" t="n">
-        <v>-27.763090426255</v>
+        <v>-27.7630916885089</v>
       </c>
       <c r="I54" t="n">
-        <v>313.49123380014</v>
+        <v>313.491233636894</v>
       </c>
       <c r="J54" t="n">
         <v>1309.18056330287</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="55">
@@ -5704,31 +5704,31 @@
         <v>26.2763956711515</v>
       </c>
       <c r="C55" t="n">
-        <v>-256.934632713396</v>
+        <v>-256.934630252053</v>
       </c>
       <c r="D55" t="n">
-        <v>350.956707500247</v>
+        <v>350.956708780495</v>
       </c>
       <c r="E55" t="n">
-        <v>1345.85582183342</v>
+        <v>1345.85582587152</v>
       </c>
       <c r="F55" t="n">
         <v>1309.18056330287</v>
       </c>
       <c r="G55" t="n">
-        <v>-36.6752585305469</v>
+        <v>-36.6752625686433</v>
       </c>
       <c r="H55" t="n">
-        <v>-8.78477926586222</v>
+        <v>-8.78478047703651</v>
       </c>
       <c r="I55" t="n">
-        <v>342.171928234385</v>
+        <v>342.171928303459</v>
       </c>
       <c r="J55" t="n">
         <v>1309.18056330287</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="56">
@@ -5739,31 +5739,31 @@
         <v>25.6964392390321</v>
       </c>
       <c r="C56" t="n">
-        <v>-256.934632713396</v>
+        <v>-256.934630252053</v>
       </c>
       <c r="D56" t="n">
-        <v>346.781185131151</v>
+        <v>346.781186333401</v>
       </c>
       <c r="E56" t="n">
-        <v>1345.85582183342</v>
+        <v>1345.85582587152</v>
       </c>
       <c r="F56" t="n">
         <v>1309.18056330287</v>
       </c>
       <c r="G56" t="n">
-        <v>-36.6752585305469</v>
+        <v>-36.6752625686433</v>
       </c>
       <c r="H56" t="n">
-        <v>0.32034094755951</v>
+        <v>0.320339963575217</v>
       </c>
       <c r="I56" t="n">
-        <v>347.10152607871</v>
+        <v>347.101526296976</v>
       </c>
       <c r="J56" t="n">
         <v>1309.18056330287</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="57">
@@ -5774,31 +5774,31 @@
         <v>20.1521132075917</v>
       </c>
       <c r="C57" t="n">
-        <v>-256.934632713396</v>
+        <v>-256.934630252053</v>
       </c>
       <c r="D57" t="n">
-        <v>306.863604975626</v>
+        <v>306.863605432217</v>
       </c>
       <c r="E57" t="n">
-        <v>1345.85582183342</v>
+        <v>1345.85582587152</v>
       </c>
       <c r="F57" t="n">
         <v>1309.18056330287</v>
       </c>
       <c r="G57" t="n">
-        <v>-36.6752585305469</v>
+        <v>-36.6752625686433</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.447729785989848</v>
+        <v>-0.447730366673692</v>
       </c>
       <c r="I57" t="n">
-        <v>306.415875189636</v>
+        <v>306.415875065543</v>
       </c>
       <c r="J57" t="n">
         <v>1309.18056330287</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="58">
@@ -5809,31 +5809,31 @@
         <v>15.247323626023</v>
       </c>
       <c r="C58" t="n">
-        <v>-250.284565731111</v>
+        <v>-250.284564255465</v>
       </c>
       <c r="D58" t="n">
-        <v>272.932683126163</v>
+        <v>272.932682695799</v>
       </c>
       <c r="E58" t="n">
-        <v>1169.73183634626</v>
+        <v>1169.73183608186</v>
       </c>
       <c r="F58" t="n">
         <v>1129.49132682075</v>
       </c>
       <c r="G58" t="n">
-        <v>-40.2405095255099</v>
+        <v>-40.2405092611111</v>
       </c>
       <c r="H58" t="n">
-        <v>-11.0889914665103</v>
+        <v>-11.0889914677832</v>
       </c>
       <c r="I58" t="n">
-        <v>261.843691659652</v>
+        <v>261.843691228016</v>
       </c>
       <c r="J58" t="n">
         <v>1129.49132682075</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="59">
@@ -5844,31 +5844,31 @@
         <v>14.973474992244</v>
       </c>
       <c r="C59" t="n">
-        <v>-250.284565731111</v>
+        <v>-250.284564255465</v>
       </c>
       <c r="D59" t="n">
-        <v>270.961050374523</v>
+        <v>270.961049907329</v>
       </c>
       <c r="E59" t="n">
-        <v>1169.73183634626</v>
+        <v>1169.73183608186</v>
       </c>
       <c r="F59" t="n">
         <v>1129.49132682075</v>
       </c>
       <c r="G59" t="n">
-        <v>-40.2405095255099</v>
+        <v>-40.2405092611111</v>
       </c>
       <c r="H59" t="n">
-        <v>-14.9339505046654</v>
+        <v>-14.9339502472249</v>
       </c>
       <c r="I59" t="n">
-        <v>256.027099869858</v>
+        <v>256.027099660104</v>
       </c>
       <c r="J59" t="n">
         <v>1129.49132682075</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="60">
@@ -5879,31 +5879,31 @@
         <v>20.1965764001429</v>
       </c>
       <c r="C60" t="n">
-        <v>-250.284565731111</v>
+        <v>-250.284564255465</v>
       </c>
       <c r="D60" t="n">
-        <v>308.565904044371</v>
+        <v>308.565904279634</v>
       </c>
       <c r="E60" t="n">
-        <v>1169.73183634626</v>
+        <v>1169.73183608186</v>
       </c>
       <c r="F60" t="n">
         <v>1129.49132682075</v>
       </c>
       <c r="G60" t="n">
-        <v>-40.2405095255099</v>
+        <v>-40.2405092611111</v>
       </c>
       <c r="H60" t="n">
-        <v>-11.9826069004552</v>
+        <v>-11.9826067049987</v>
       </c>
       <c r="I60" t="n">
-        <v>296.583297143916</v>
+        <v>296.583297574635</v>
       </c>
       <c r="J60" t="n">
         <v>1129.49132682075</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="61">
@@ -5914,31 +5914,31 @@
         <v>21.40583148198</v>
       </c>
       <c r="C61" t="n">
-        <v>-250.284565731111</v>
+        <v>-250.284564255465</v>
       </c>
       <c r="D61" t="n">
-        <v>317.272198801205</v>
+        <v>317.272199199101</v>
       </c>
       <c r="E61" t="n">
-        <v>1169.73183634626</v>
+        <v>1169.73183608186</v>
       </c>
       <c r="F61" t="n">
         <v>1129.49132682075</v>
       </c>
       <c r="G61" t="n">
-        <v>-40.2405095255099</v>
+        <v>-40.2405092611111</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.23496065387969</v>
+        <v>-2.23496084110471</v>
       </c>
       <c r="I61" t="n">
-        <v>315.037238147325</v>
+        <v>315.037238357997</v>
       </c>
       <c r="J61" t="n">
         <v>1129.49132682075</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.000000000000909494701772928</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="62">
@@ -5949,31 +5949,31 @@
         <v>21.7281456443213</v>
       </c>
       <c r="C62" t="n">
-        <v>-248.321110121123</v>
+        <v>-248.321105252213</v>
       </c>
       <c r="D62" t="n">
-        <v>320.000862164251</v>
+        <v>320.00086330414</v>
       </c>
       <c r="E62" t="n">
-        <v>1301.19272325491</v>
+        <v>1301.19272821028</v>
       </c>
       <c r="F62" t="n">
         <v>1405.07199875742</v>
       </c>
       <c r="G62" t="n">
-        <v>103.879275502512</v>
+        <v>103.879270547139</v>
       </c>
       <c r="H62" t="n">
-        <v>14.3089882350612</v>
+        <v>14.3089873444572</v>
       </c>
       <c r="I62" t="n">
-        <v>334.309850399312</v>
+        <v>334.309850648598</v>
       </c>
       <c r="J62" t="n">
         <v>1405.07199875742</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="63">
@@ -5984,31 +5984,31 @@
         <v>22.4909049724837</v>
       </c>
       <c r="C63" t="n">
-        <v>-248.321110121123</v>
+        <v>-248.321105252213</v>
       </c>
       <c r="D63" t="n">
-        <v>325.492513710108</v>
+        <v>325.492514952582</v>
       </c>
       <c r="E63" t="n">
-        <v>1301.19272325491</v>
+        <v>1301.19272821028</v>
       </c>
       <c r="F63" t="n">
         <v>1405.07199875742</v>
       </c>
       <c r="G63" t="n">
-        <v>103.879275502512</v>
+        <v>103.879270547139</v>
       </c>
       <c r="H63" t="n">
-        <v>25.5909000468642</v>
+        <v>25.5908987356129</v>
       </c>
       <c r="I63" t="n">
-        <v>351.083413756972</v>
+        <v>351.083413688194</v>
       </c>
       <c r="J63" t="n">
         <v>1405.07199875742</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="64">
@@ -6019,31 +6019,31 @@
         <v>22.2741530256175</v>
       </c>
       <c r="C64" t="n">
-        <v>-248.321110121123</v>
+        <v>-248.321105252213</v>
       </c>
       <c r="D64" t="n">
-        <v>323.931960964141</v>
+        <v>323.931962177463</v>
       </c>
       <c r="E64" t="n">
-        <v>1301.19272325491</v>
+        <v>1301.19272821028</v>
       </c>
       <c r="F64" t="n">
         <v>1405.07199875742</v>
       </c>
       <c r="G64" t="n">
-        <v>103.879275502512</v>
+        <v>103.879270547139</v>
       </c>
       <c r="H64" t="n">
-        <v>31.6107747815294</v>
+        <v>31.6107733323625</v>
       </c>
       <c r="I64" t="n">
-        <v>355.542735745671</v>
+        <v>355.542735509826</v>
       </c>
       <c r="J64" t="n">
         <v>1405.07199875742</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="65">
@@ -6054,31 +6054,31 @@
         <v>23.3624492883955</v>
       </c>
       <c r="C65" t="n">
-        <v>-248.321110121123</v>
+        <v>-248.321105252213</v>
       </c>
       <c r="D65" t="n">
-        <v>331.767386416406</v>
+        <v>331.767387776093</v>
       </c>
       <c r="E65" t="n">
-        <v>1301.19272325491</v>
+        <v>1301.19272821028</v>
       </c>
       <c r="F65" t="n">
         <v>1405.07199875742</v>
       </c>
       <c r="G65" t="n">
-        <v>103.879275502512</v>
+        <v>103.879270547139</v>
       </c>
       <c r="H65" t="n">
-        <v>32.3686124390568</v>
+        <v>32.368611134706</v>
       </c>
       <c r="I65" t="n">
-        <v>364.135998855462</v>
+        <v>364.135998910799</v>
       </c>
       <c r="J65" t="n">
         <v>1405.07199875742</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.000000000000682121026329696</v>
+        <v>-0.000000000000454747350886464</v>
       </c>
     </row>
     <row r="66">
@@ -6089,31 +6089,31 @@
         <v>26.3010438508106</v>
       </c>
       <c r="C66" t="n">
-        <v>-102.568955069101</v>
+        <v>-102.568952625382</v>
       </c>
       <c r="D66" t="n">
-        <v>383.218150333604</v>
+        <v>383.218151092696</v>
       </c>
       <c r="E66" t="n">
-        <v>1474.39022900073</v>
+        <v>1474.39023094465</v>
       </c>
       <c r="F66" t="n">
         <v>1566.19311812443</v>
       </c>
       <c r="G66" t="n">
-        <v>91.8028891237007</v>
+        <v>91.8028871797785</v>
       </c>
       <c r="H66" t="n">
-        <v>27.8644130194465</v>
+        <v>27.8644121426433</v>
       </c>
       <c r="I66" t="n">
-        <v>411.08256335305</v>
+        <v>411.08256323534</v>
       </c>
       <c r="J66" t="n">
         <v>1566.19311812443</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -6124,31 +6124,31 @@
         <v>25.8041762528243</v>
       </c>
       <c r="C67" t="n">
-        <v>-102.568955069101</v>
+        <v>-102.568952625382</v>
       </c>
       <c r="D67" t="n">
-        <v>379.640844082703</v>
+        <v>379.640844774972</v>
       </c>
       <c r="E67" t="n">
-        <v>1474.39022900073</v>
+        <v>1474.39023094465</v>
       </c>
       <c r="F67" t="n">
         <v>1566.19311812443</v>
       </c>
       <c r="G67" t="n">
-        <v>91.8028891237007</v>
+        <v>91.8028871797785</v>
       </c>
       <c r="H67" t="n">
-        <v>24.0972569561938</v>
+        <v>24.0972564067388</v>
       </c>
       <c r="I67" t="n">
-        <v>403.738101038897</v>
+        <v>403.738101181711</v>
       </c>
       <c r="J67" t="n">
         <v>1566.19311812443</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -6159,31 +6159,31 @@
         <v>20.9236846319188</v>
       </c>
       <c r="C68" t="n">
-        <v>-102.568955069101</v>
+        <v>-102.568952625382</v>
       </c>
       <c r="D68" t="n">
-        <v>344.502684030226</v>
+        <v>344.502684066116</v>
       </c>
       <c r="E68" t="n">
-        <v>1474.39022900073</v>
+        <v>1474.39023094465</v>
       </c>
       <c r="F68" t="n">
         <v>1566.19311812443</v>
       </c>
       <c r="G68" t="n">
-        <v>91.8028891237007</v>
+        <v>91.8028871797785</v>
       </c>
       <c r="H68" t="n">
-        <v>21.0671442492987</v>
+        <v>21.0671439269923</v>
       </c>
       <c r="I68" t="n">
-        <v>365.569828279525</v>
+        <v>365.569827993108</v>
       </c>
       <c r="J68" t="n">
         <v>1566.19311812443</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6194,31 +6194,31 @@
         <v>24.0524000415956</v>
       </c>
       <c r="C69" t="n">
-        <v>-102.568955069101</v>
+        <v>-102.568952625382</v>
       </c>
       <c r="D69" t="n">
-        <v>367.028550554197</v>
+        <v>367.028551010868</v>
       </c>
       <c r="E69" t="n">
-        <v>1474.39022900073</v>
+        <v>1474.39023094465</v>
       </c>
       <c r="F69" t="n">
         <v>1566.19311812443</v>
       </c>
       <c r="G69" t="n">
-        <v>91.8028891237007</v>
+        <v>91.8028871797785</v>
       </c>
       <c r="H69" t="n">
-        <v>18.7740748987614</v>
+        <v>18.774074703404</v>
       </c>
       <c r="I69" t="n">
-        <v>385.802625452958</v>
+        <v>385.802625714272</v>
       </c>
       <c r="J69" t="n">
         <v>1566.19311812443</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6229,31 +6229,31 @@
         <v>26.4067696723934</v>
       </c>
       <c r="C70" t="n">
-        <v>6.52951355258347</v>
+        <v>6.52951502452152</v>
       </c>
       <c r="D70" t="n">
-        <v>406.654810597039</v>
+        <v>406.654810800289</v>
       </c>
       <c r="E70" t="n">
-        <v>1595.41629571738</v>
+        <v>1595.41629594751</v>
       </c>
       <c r="F70" t="n">
         <v>1626.78805854904</v>
       </c>
       <c r="G70" t="n">
-        <v>31.3717628316631</v>
+        <v>31.3717626015309</v>
       </c>
       <c r="H70" t="n">
-        <v>17.2180489045817</v>
+        <v>17.2180487359739</v>
       </c>
       <c r="I70" t="n">
-        <v>423.87285950162</v>
+        <v>423.872859536263</v>
       </c>
       <c r="J70" t="n">
         <v>1626.78805854904</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="71">
@@ -6264,31 +6264,31 @@
         <v>26.2388712502691</v>
       </c>
       <c r="C71" t="n">
-        <v>6.52951355258347</v>
+        <v>6.52951502452152</v>
       </c>
       <c r="D71" t="n">
-        <v>405.445989419293</v>
+        <v>405.445989599963</v>
       </c>
       <c r="E71" t="n">
-        <v>1595.41629571738</v>
+        <v>1595.41629594751</v>
       </c>
       <c r="F71" t="n">
         <v>1626.78805854904</v>
       </c>
       <c r="G71" t="n">
-        <v>31.3717628316631</v>
+        <v>31.3717626015309</v>
       </c>
       <c r="H71" t="n">
-        <v>12.8455952282434</v>
+        <v>12.8455951147653</v>
       </c>
       <c r="I71" t="n">
-        <v>418.291584647536</v>
+        <v>418.291584714728</v>
       </c>
       <c r="J71" t="n">
         <v>1626.78805854904</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="72">
@@ -6299,31 +6299,31 @@
         <v>22.9500627992814</v>
       </c>
       <c r="C72" t="n">
-        <v>6.52951355258347</v>
+        <v>6.52951502452152</v>
       </c>
       <c r="D72" t="n">
-        <v>381.767498253007</v>
+        <v>381.767497991363</v>
       </c>
       <c r="E72" t="n">
-        <v>1595.41629571738</v>
+        <v>1595.41629594751</v>
       </c>
       <c r="F72" t="n">
         <v>1626.78805854904</v>
       </c>
       <c r="G72" t="n">
-        <v>31.3717628316631</v>
+        <v>31.3717626015309</v>
       </c>
       <c r="H72" t="n">
-        <v>5.65671386974656</v>
+        <v>5.65671383977844</v>
       </c>
       <c r="I72" t="n">
-        <v>387.424212122753</v>
+        <v>387.424211831142</v>
       </c>
       <c r="J72" t="n">
         <v>1626.78805854904</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="73">
@@ -6334,31 +6334,31 @@
         <v>25.6974622201534</v>
       </c>
       <c r="C73" t="n">
-        <v>6.52951355258347</v>
+        <v>6.52951502452152</v>
       </c>
       <c r="D73" t="n">
-        <v>401.547997448039</v>
+        <v>401.547997555894</v>
       </c>
       <c r="E73" t="n">
-        <v>1595.41629571738</v>
+        <v>1595.41629594751</v>
       </c>
       <c r="F73" t="n">
         <v>1626.78805854904</v>
       </c>
       <c r="G73" t="n">
-        <v>31.3717628316631</v>
+        <v>31.3717626015309</v>
       </c>
       <c r="H73" t="n">
-        <v>-4.3485951709089</v>
+        <v>-4.34859508898683</v>
       </c>
       <c r="I73" t="n">
-        <v>397.19940227713</v>
+        <v>397.199402466907</v>
       </c>
       <c r="J73" t="n">
         <v>1626.78805854904</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="74">
@@ -6369,31 +6369,31 @@
         <v>23.6361191870476</v>
       </c>
       <c r="C74" t="n">
-        <v>36.8002441990616</v>
+        <v>36.800245104545</v>
       </c>
       <c r="D74" t="n">
-        <v>392.998500639789</v>
+        <v>392.99850025055</v>
       </c>
       <c r="E74" t="n">
-        <v>1611.27222780412</v>
+        <v>1611.27222698088</v>
       </c>
       <c r="F74" t="n">
         <v>1572.138</v>
       </c>
       <c r="G74" t="n">
-        <v>-39.1342278041209</v>
+        <v>-39.1342269808817</v>
       </c>
       <c r="H74" t="n">
-        <v>-17.170331893723</v>
+        <v>-17.1703316715305</v>
       </c>
       <c r="I74" t="n">
-        <v>375.828168746066</v>
+        <v>375.828168579019</v>
       </c>
       <c r="J74" t="n">
         <v>1572.138</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="75">
@@ -6404,31 +6404,31 @@
         <v>25.3564552861445</v>
       </c>
       <c r="C75" t="n">
-        <v>36.8002441990616</v>
+        <v>36.800245104545</v>
       </c>
       <c r="D75" t="n">
-        <v>405.384434248441</v>
+        <v>405.384434090571</v>
       </c>
       <c r="E75" t="n">
-        <v>1611.27222780412</v>
+        <v>1611.27222698088</v>
       </c>
       <c r="F75" t="n">
         <v>1572.138</v>
       </c>
       <c r="G75" t="n">
-        <v>-39.1342278041209</v>
+        <v>-39.1342269808817</v>
       </c>
       <c r="H75" t="n">
-        <v>-19.3443166057715</v>
+        <v>-19.3443163340239</v>
       </c>
       <c r="I75" t="n">
-        <v>386.040117642669</v>
+        <v>386.040117756547</v>
       </c>
       <c r="J75" t="n">
         <v>1572.138</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="76">
@@ -6439,31 +6439,31 @@
         <v>25.1027329943762</v>
       </c>
       <c r="C76" t="n">
-        <v>36.8002441990616</v>
+        <v>36.800245104545</v>
       </c>
       <c r="D76" t="n">
-        <v>403.557705469962</v>
+        <v>403.557705277969</v>
       </c>
       <c r="E76" t="n">
-        <v>1611.27222780412</v>
+        <v>1611.27222698088</v>
       </c>
       <c r="F76" t="n">
         <v>1572.138</v>
       </c>
       <c r="G76" t="n">
-        <v>-39.1342278041209</v>
+        <v>-39.1342269808817</v>
       </c>
       <c r="H76" t="n">
-        <v>-10.8705493070546</v>
+        <v>-10.8705490764672</v>
       </c>
       <c r="I76" t="n">
-        <v>392.687156162907</v>
+        <v>392.687156201502</v>
       </c>
       <c r="J76" t="n">
         <v>1572.138</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="77">
@@ -6474,31 +6474,31 @@
         <v>25.9046925324318</v>
       </c>
       <c r="C77" t="n">
-        <v>36.8002441990616</v>
+        <v>36.800245104545</v>
       </c>
       <c r="D77" t="n">
-        <v>409.331587445929</v>
+        <v>409.331587361792</v>
       </c>
       <c r="E77" t="n">
-        <v>1611.27222780412</v>
+        <v>1611.27222698088</v>
       </c>
       <c r="F77" t="n">
         <v>1572.138</v>
       </c>
       <c r="G77" t="n">
-        <v>-39.1342278041209</v>
+        <v>-39.1342269808817</v>
       </c>
       <c r="H77" t="n">
-        <v>8.25097000242775</v>
+        <v>8.2509701011396</v>
       </c>
       <c r="I77" t="n">
-        <v>417.582557448357</v>
+        <v>417.582557462932</v>
       </c>
       <c r="J77" t="n">
         <v>1572.138</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="78">
@@ -6509,31 +6509,31 @@
         <v>26.8069768911658</v>
       </c>
       <c r="C78" t="n">
-        <v>-8.53938511920455</v>
+        <v>-8.53938403980283</v>
       </c>
       <c r="D78" t="n">
-        <v>406.404208972876</v>
+        <v>406.404209199204</v>
       </c>
       <c r="E78" t="n">
-        <v>1618.37384883024</v>
+        <v>1618.37384960025</v>
       </c>
       <c r="F78" t="n">
         <v>1799.159</v>
       </c>
       <c r="G78" t="n">
-        <v>180.785151169764</v>
+        <v>180.785150399749</v>
       </c>
       <c r="H78" t="n">
-        <v>38.0202413226756</v>
+        <v>38.0202411987966</v>
       </c>
       <c r="I78" t="n">
-        <v>444.424450295551</v>
+        <v>444.424450398001</v>
       </c>
       <c r="J78" t="n">
         <v>1799.159</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="79">
@@ -6544,31 +6544,31 @@
         <v>27.0678469006352</v>
       </c>
       <c r="C79" t="n">
-        <v>-8.53938511920455</v>
+        <v>-8.53938403980283</v>
       </c>
       <c r="D79" t="n">
-        <v>408.282399298285</v>
+        <v>408.282399559698</v>
       </c>
       <c r="E79" t="n">
-        <v>1618.37384883024</v>
+        <v>1618.37384960025</v>
       </c>
       <c r="F79" t="n">
         <v>1799.159</v>
       </c>
       <c r="G79" t="n">
-        <v>180.785151169764</v>
+        <v>180.785150399749</v>
       </c>
       <c r="H79" t="n">
-        <v>52.7983684386809</v>
+        <v>52.7983681983157</v>
       </c>
       <c r="I79" t="n">
-        <v>461.080767736966</v>
+        <v>461.080767758014</v>
       </c>
       <c r="J79" t="n">
         <v>1799.159</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="80">
@@ -6579,31 +6579,31 @@
         <v>25.0370918835188</v>
       </c>
       <c r="C80" t="n">
-        <v>-8.53938511920455</v>
+        <v>-8.53938403980283</v>
       </c>
       <c r="D80" t="n">
-        <v>393.661537229155</v>
+        <v>393.661537217451</v>
       </c>
       <c r="E80" t="n">
-        <v>1618.37384883024</v>
+        <v>1618.37384960025</v>
       </c>
       <c r="F80" t="n">
         <v>1799.159</v>
       </c>
       <c r="G80" t="n">
-        <v>180.785151169764</v>
+        <v>180.785150399749</v>
       </c>
       <c r="H80" t="n">
-        <v>52.5853513504436</v>
+        <v>52.5853510996968</v>
       </c>
       <c r="I80" t="n">
-        <v>446.246888579598</v>
+        <v>446.246888317147</v>
       </c>
       <c r="J80" t="n">
         <v>1799.159</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="81">
@@ -6614,31 +6614,31 @@
         <v>27.3099819670809</v>
       </c>
       <c r="C81" t="n">
-        <v>-8.53938511920455</v>
+        <v>-8.53938403980283</v>
       </c>
       <c r="D81" t="n">
-        <v>410.02570332992</v>
+        <v>410.025703623898</v>
       </c>
       <c r="E81" t="n">
-        <v>1618.37384883024</v>
+        <v>1618.37384960025</v>
       </c>
       <c r="F81" t="n">
         <v>1799.159</v>
       </c>
       <c r="G81" t="n">
-        <v>180.785151169764</v>
+        <v>180.785150399749</v>
       </c>
       <c r="H81" t="n">
-        <v>37.3811900579637</v>
+        <v>37.3811899029401</v>
       </c>
       <c r="I81" t="n">
-        <v>447.406893387884</v>
+        <v>447.406893526838</v>
       </c>
       <c r="J81" t="n">
         <v>1799.159</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.000000000000454747350886464</v>
+        <v>-0.000000000000227373675443232</v>
       </c>
     </row>
     <row r="82">
@@ -6649,25 +6649,25 @@
         <v>30.2678629991828</v>
       </c>
       <c r="C82" t="n">
-        <v>173.685710662393</v>
+        <v>173.685710905009</v>
       </c>
       <c r="D82" t="n">
-        <v>469.196006979511</v>
+        <v>469.196006882573</v>
       </c>
       <c r="E82" t="n">
-        <v>1857.57564261225</v>
+        <v>1857.57564186569</v>
       </c>
       <c r="F82" t="n">
         <v>1837.48745054851</v>
       </c>
       <c r="G82" t="n">
-        <v>-20.0881920637353</v>
+        <v>-20.0881913171741</v>
       </c>
       <c r="H82" t="n">
-        <v>7.18588456124127</v>
+        <v>7.18588460804537</v>
       </c>
       <c r="I82" t="n">
-        <v>476.381891540752</v>
+        <v>476.381891490619</v>
       </c>
       <c r="J82" t="n">
         <v>1837.48745054851</v>
@@ -6684,25 +6684,25 @@
         <v>30.0759732328241</v>
       </c>
       <c r="C83" t="n">
-        <v>173.685710662393</v>
+        <v>173.685710905009</v>
       </c>
       <c r="D83" t="n">
-        <v>467.814454905154</v>
+        <v>467.814454782409</v>
       </c>
       <c r="E83" t="n">
-        <v>1857.57564261225</v>
+        <v>1857.57564186569</v>
       </c>
       <c r="F83" t="n">
         <v>1837.48745054851</v>
       </c>
       <c r="G83" t="n">
-        <v>-20.0881920637353</v>
+        <v>-20.0881913171741</v>
       </c>
       <c r="H83" t="n">
-        <v>-9.77541066831779</v>
+        <v>-9.77541048484809</v>
       </c>
       <c r="I83" t="n">
-        <v>458.039044236836</v>
+        <v>458.039044297561</v>
       </c>
       <c r="J83" t="n">
         <v>1837.48745054851</v>
@@ -6719,25 +6719,25 @@
         <v>28.1027332639806</v>
       </c>
       <c r="C84" t="n">
-        <v>173.685710662393</v>
+        <v>173.685710905009</v>
       </c>
       <c r="D84" t="n">
-        <v>453.607684925226</v>
+        <v>453.6076845371</v>
       </c>
       <c r="E84" t="n">
-        <v>1857.57564261225</v>
+        <v>1857.57564186569</v>
       </c>
       <c r="F84" t="n">
         <v>1837.48745054851</v>
       </c>
       <c r="G84" t="n">
-        <v>-20.0881920637353</v>
+        <v>-20.0881913171741</v>
       </c>
       <c r="H84" t="n">
-        <v>-13.5026956307134</v>
+        <v>-13.5026953757403</v>
       </c>
       <c r="I84" t="n">
-        <v>440.104989294513</v>
+        <v>440.104989161359</v>
       </c>
       <c r="J84" t="n">
         <v>1837.48745054851</v>
@@ -6754,25 +6754,25 @@
         <v>29.9569464620881</v>
       </c>
       <c r="C85" t="n">
-        <v>173.685710662393</v>
+        <v>173.685710905009</v>
       </c>
       <c r="D85" t="n">
-        <v>466.957495802359</v>
+        <v>466.957495663606</v>
       </c>
       <c r="E85" t="n">
-        <v>1857.57564261225</v>
+        <v>1857.57564186569</v>
       </c>
       <c r="F85" t="n">
         <v>1837.48745054851</v>
       </c>
       <c r="G85" t="n">
-        <v>-20.0881920637353</v>
+        <v>-20.0881913171741</v>
       </c>
       <c r="H85" t="n">
-        <v>-3.99597032594569</v>
+        <v>-3.99597006463132</v>
       </c>
       <c r="I85" t="n">
-        <v>462.961525476413</v>
+        <v>462.961525598975</v>
       </c>
       <c r="J85" t="n">
         <v>1837.48745054851</v>
@@ -6789,25 +6789,25 @@
         <v>31.9492837695939</v>
       </c>
       <c r="C86" t="n">
-        <v>124.309952839589</v>
+        <v>124.309951443895</v>
       </c>
       <c r="D86" t="n">
-        <v>471.039305252728</v>
+        <v>471.039305207999</v>
       </c>
       <c r="E86" t="n">
-        <v>1855.25489645174</v>
+        <v>1855.25489573293</v>
       </c>
       <c r="F86" t="n">
         <v>2009.72567286795</v>
       </c>
       <c r="G86" t="n">
-        <v>154.470776416211</v>
+        <v>154.470777135021</v>
       </c>
       <c r="H86" t="n">
-        <v>18.7447652459855</v>
+        <v>18.7447654484789</v>
       </c>
       <c r="I86" t="n">
-        <v>489.784070498713</v>
+        <v>489.784070656478</v>
       </c>
       <c r="J86" t="n">
         <v>2009.72567286795</v>
@@ -6824,25 +6824,25 @@
         <v>30.5324798214385</v>
       </c>
       <c r="C87" t="n">
-        <v>124.309952839589</v>
+        <v>124.309951443895</v>
       </c>
       <c r="D87" t="n">
-        <v>460.838717328344</v>
+        <v>460.838717093069</v>
       </c>
       <c r="E87" t="n">
-        <v>1855.25489645174</v>
+        <v>1855.25489573293</v>
       </c>
       <c r="F87" t="n">
         <v>2009.72567286795</v>
       </c>
       <c r="G87" t="n">
-        <v>154.470776416211</v>
+        <v>154.470777135021</v>
       </c>
       <c r="H87" t="n">
-        <v>35.7902310179848</v>
+        <v>35.7902311878335</v>
       </c>
       <c r="I87" t="n">
-        <v>496.628948346329</v>
+        <v>496.628948280902</v>
       </c>
       <c r="J87" t="n">
         <v>2009.72567286795</v>
@@ -6859,25 +6859,25 @@
         <v>28.1619781201749</v>
       </c>
       <c r="C88" t="n">
-        <v>124.309952839589</v>
+        <v>124.309951443895</v>
       </c>
       <c r="D88" t="n">
-        <v>443.771775172992</v>
+        <v>443.771774618907</v>
       </c>
       <c r="E88" t="n">
-        <v>1855.25489645174</v>
+        <v>1855.25489573293</v>
       </c>
       <c r="F88" t="n">
         <v>2009.72567286795</v>
       </c>
       <c r="G88" t="n">
-        <v>154.470776416211</v>
+        <v>154.470777135021</v>
       </c>
       <c r="H88" t="n">
-        <v>47.1404269900524</v>
+        <v>47.1404271534325</v>
       </c>
       <c r="I88" t="n">
-        <v>490.912202163045</v>
+        <v>490.91220177234</v>
       </c>
       <c r="J88" t="n">
         <v>2009.72567286795</v>
@@ -6894,25 +6894,25 @@
         <v>33.1390240141613</v>
       </c>
       <c r="C89" t="n">
-        <v>124.309952839589</v>
+        <v>124.309951443895</v>
       </c>
       <c r="D89" t="n">
-        <v>479.605098697677</v>
+        <v>479.605098812957</v>
       </c>
       <c r="E89" t="n">
-        <v>1855.25489645174</v>
+        <v>1855.25489573293</v>
       </c>
       <c r="F89" t="n">
         <v>2009.72567286795</v>
       </c>
       <c r="G89" t="n">
-        <v>154.470776416211</v>
+        <v>154.470777135021</v>
       </c>
       <c r="H89" t="n">
-        <v>52.7953531621883</v>
+        <v>52.7953533452759</v>
       </c>
       <c r="I89" t="n">
-        <v>532.400451859865</v>
+        <v>532.400452158233</v>
       </c>
       <c r="J89" t="n">
         <v>2009.72567286795</v>
@@ -6929,25 +6929,25 @@
         <v>33.8087363054348</v>
       </c>
       <c r="C90" t="n">
-        <v>257.81909744158</v>
+        <v>257.819095322429</v>
       </c>
       <c r="D90" t="n">
-        <v>512.175915128454</v>
+        <v>512.175914732997</v>
       </c>
       <c r="E90" t="n">
-        <v>2034.40137817368</v>
+        <v>2034.40137632468</v>
       </c>
       <c r="F90" t="n">
         <v>2198.14869083481</v>
       </c>
       <c r="G90" t="n">
-        <v>163.747312661131</v>
+        <v>163.747314510126</v>
       </c>
       <c r="H90" t="n">
-        <v>52.7550095343924</v>
+        <v>52.7550097633637</v>
       </c>
       <c r="I90" t="n">
-        <v>564.930924662846</v>
+        <v>564.93092449636</v>
       </c>
       <c r="J90" t="n">
         <v>2198.14869083481</v>
@@ -6964,25 +6964,25 @@
         <v>35.1368582395621</v>
       </c>
       <c r="C91" t="n">
-        <v>257.81909744158</v>
+        <v>257.819095322429</v>
       </c>
       <c r="D91" t="n">
-        <v>521.738017620479</v>
+        <v>521.738017403641</v>
       </c>
       <c r="E91" t="n">
-        <v>2034.40137817368</v>
+        <v>2034.40137632468</v>
       </c>
       <c r="F91" t="n">
         <v>2198.14869083481</v>
       </c>
       <c r="G91" t="n">
-        <v>163.747312661131</v>
+        <v>163.747314510126</v>
       </c>
       <c r="H91" t="n">
-        <v>48.0115995356302</v>
+        <v>48.011599876266</v>
       </c>
       <c r="I91" t="n">
-        <v>569.749617156109</v>
+        <v>569.749617279907</v>
       </c>
       <c r="J91" t="n">
         <v>2198.14869083481</v>
@@ -6999,25 +6999,25 @@
         <v>31.6775239815922</v>
       </c>
       <c r="C92" t="n">
-        <v>257.81909744158</v>
+        <v>257.819095322429</v>
       </c>
       <c r="D92" t="n">
-        <v>496.83178884818</v>
+        <v>496.831788166095</v>
       </c>
       <c r="E92" t="n">
-        <v>2034.40137817368</v>
+        <v>2034.40137632468</v>
       </c>
       <c r="F92" t="n">
         <v>2198.14869083481</v>
       </c>
       <c r="G92" t="n">
-        <v>163.747312661131</v>
+        <v>163.747314510126</v>
       </c>
       <c r="H92" t="n">
-        <v>38.5651231659018</v>
+        <v>38.5651236839826</v>
       </c>
       <c r="I92" t="n">
-        <v>535.396912014082</v>
+        <v>535.396911850078</v>
       </c>
       <c r="J92" t="n">
         <v>2198.14869083481</v>
@@ -7034,25 +7034,25 @@
         <v>32.625320599879</v>
       </c>
       <c r="C93" t="n">
-        <v>257.81909744158</v>
+        <v>257.819095322429</v>
       </c>
       <c r="D93" t="n">
-        <v>503.655656576566</v>
+        <v>503.655656021951</v>
       </c>
       <c r="E93" t="n">
-        <v>2034.40137817368</v>
+        <v>2034.40137632468</v>
       </c>
       <c r="F93" t="n">
         <v>2198.14869083481</v>
       </c>
       <c r="G93" t="n">
-        <v>163.747312661131</v>
+        <v>163.747314510126</v>
       </c>
       <c r="H93" t="n">
-        <v>24.4155804252071</v>
+        <v>24.4155811865136</v>
       </c>
       <c r="I93" t="n">
-        <v>528.071237001773</v>
+        <v>528.071237208465</v>
       </c>
       <c r="J93" t="n">
         <v>2198.14869083481</v>
@@ -7066,28 +7066,28 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>30.6161933310345</v>
+        <v>30.6161933311176</v>
       </c>
       <c r="C94" t="n">
-        <v>378.09194267838</v>
+        <v>378.091939286187</v>
       </c>
       <c r="D94" t="n">
-        <v>514.188499766468</v>
+        <v>514.188498271866</v>
       </c>
       <c r="E94" t="n">
-        <v>2089.55458386489</v>
+        <v>2089.55457850211</v>
       </c>
       <c r="F94" t="n">
         <v>2045.82233722826</v>
       </c>
       <c r="G94" t="n">
-        <v>-43.7322466366288</v>
+        <v>-43.7322412738547</v>
       </c>
       <c r="H94" t="n">
-        <v>5.56297131354615</v>
+        <v>5.56297238385909</v>
       </c>
       <c r="I94" t="n">
-        <v>519.751471080014</v>
+        <v>519.751470655725</v>
       </c>
       <c r="J94" t="n">
         <v>2045.82233722826</v>
@@ -7101,28 +7101,28 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>32.0118849853594</v>
+        <v>32.011884985538</v>
       </c>
       <c r="C95" t="n">
-        <v>378.09194267838</v>
+        <v>378.091939286187</v>
       </c>
       <c r="D95" t="n">
-        <v>524.237085143299</v>
+        <v>524.237083837091</v>
       </c>
       <c r="E95" t="n">
-        <v>2089.55458386489</v>
+        <v>2089.55457850211</v>
       </c>
       <c r="F95" t="n">
         <v>2045.82233722826</v>
       </c>
       <c r="G95" t="n">
-        <v>-43.7322466366288</v>
+        <v>-43.7322412738547</v>
       </c>
       <c r="H95" t="n">
-        <v>-8.57648552019955</v>
+        <v>-8.57648421813183</v>
       </c>
       <c r="I95" t="n">
-        <v>515.660599623099</v>
+        <v>515.660599618959</v>
       </c>
       <c r="J95" t="n">
         <v>2045.82233722826</v>
@@ -7136,28 +7136,28 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>32.0320057364502</v>
+        <v>32.0320057366789</v>
       </c>
       <c r="C96" t="n">
-        <v>378.09194267838</v>
+        <v>378.091939286187</v>
       </c>
       <c r="D96" t="n">
-        <v>524.381948863416</v>
+        <v>524.381947560275</v>
       </c>
       <c r="E96" t="n">
-        <v>2089.55458386489</v>
+        <v>2089.55457850211</v>
       </c>
       <c r="F96" t="n">
         <v>2045.82233722826</v>
       </c>
       <c r="G96" t="n">
-        <v>-43.7322466366288</v>
+        <v>-43.7322412738547</v>
       </c>
       <c r="H96" t="n">
-        <v>-18.00279007603</v>
+        <v>-18.0027886194591</v>
       </c>
       <c r="I96" t="n">
-        <v>506.379158787386</v>
+        <v>506.379158940816</v>
       </c>
       <c r="J96" t="n">
         <v>2045.82233722826</v>
@@ -7171,28 +7171,28 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>32.3605049154058</v>
+        <v>32.3605049156537</v>
       </c>
       <c r="C97" t="n">
-        <v>378.09194267838</v>
+        <v>378.091939286187</v>
       </c>
       <c r="D97" t="n">
-        <v>526.747050091703</v>
+        <v>526.74704883288</v>
       </c>
       <c r="E97" t="n">
-        <v>2089.55458386489</v>
+        <v>2089.55457850211</v>
       </c>
       <c r="F97" t="n">
         <v>2045.82233722826</v>
       </c>
       <c r="G97" t="n">
-        <v>-43.7322466366288</v>
+        <v>-43.7322412738547</v>
       </c>
       <c r="H97" t="n">
-        <v>-22.7159423539452</v>
+        <v>-22.7159408201227</v>
       </c>
       <c r="I97" t="n">
-        <v>504.031107737758</v>
+        <v>504.031108012757</v>
       </c>
       <c r="J97" t="n">
         <v>2045.82233722826</v>
@@ -7231,13 +7231,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>323.547632548277</v>
+        <v>323.547632744127</v>
       </c>
       <c r="C2" t="n">
         <v>19.0235910981994</v>
       </c>
       <c r="D2" t="n">
-        <v>-59.8548209275739</v>
+        <v>-59.8548177000365</v>
       </c>
     </row>
     <row r="3">
@@ -7245,13 +7245,13 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>327.498294975882</v>
+        <v>327.498295167857</v>
       </c>
       <c r="C3" t="n">
         <v>19.540739677546</v>
       </c>
       <c r="D3" t="n">
-        <v>-59.8548209275739</v>
+        <v>-59.8548177000365</v>
       </c>
     </row>
     <row r="4">
@@ -7259,13 +7259,13 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>313.845887666642</v>
+        <v>313.845887448242</v>
       </c>
       <c r="C4" t="n">
         <v>17.5813453888002</v>
       </c>
       <c r="D4" t="n">
-        <v>-59.8548209275739</v>
+        <v>-59.8548177000365</v>
       </c>
     </row>
     <row r="5">
@@ -7273,13 +7273,13 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>328.942145051602</v>
+        <v>328.942144882177</v>
       </c>
       <c r="C5" t="n">
         <v>19.5834018880699</v>
       </c>
       <c r="D5" t="n">
-        <v>-59.8548209275739</v>
+        <v>-59.8548177000365</v>
       </c>
     </row>
     <row r="6">
@@ -7287,13 +7287,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>331.57857151585</v>
+        <v>331.578571696054</v>
       </c>
       <c r="C6" t="n">
         <v>21.3315046724616</v>
       </c>
       <c r="D6" t="n">
-        <v>-112.099647763188</v>
+        <v>-112.09964341958</v>
       </c>
     </row>
     <row r="7">
@@ -7301,13 +7301,13 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>335.468135029047</v>
+        <v>335.468135139372</v>
       </c>
       <c r="C7" t="n">
         <v>22.1736020548486</v>
       </c>
       <c r="D7" t="n">
-        <v>-112.099647763188</v>
+        <v>-112.09964341958</v>
       </c>
     </row>
     <row r="8">
@@ -7315,13 +7315,13 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>311.634257917617</v>
+        <v>311.634257608347</v>
       </c>
       <c r="C8" t="n">
         <v>19.5932337266586</v>
       </c>
       <c r="D8" t="n">
-        <v>-112.099647763188</v>
+        <v>-112.09964341958</v>
       </c>
     </row>
     <row r="9">
@@ -7329,13 +7329,13 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>318.82008032178</v>
+        <v>318.82008034052</v>
       </c>
       <c r="C9" t="n">
         <v>21.7494894868981</v>
       </c>
       <c r="D9" t="n">
-        <v>-112.099647763188</v>
+        <v>-112.09964341958</v>
       </c>
     </row>
     <row r="10">
@@ -7343,13 +7343,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>293.997524990506</v>
+        <v>293.997525102392</v>
       </c>
       <c r="C10" t="n">
         <v>21.6775413501649</v>
       </c>
       <c r="D10" t="n">
-        <v>-174.084999126668</v>
+        <v>-174.084996009445</v>
       </c>
     </row>
     <row r="11">
@@ -7357,13 +7357,13 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>299.432800396899</v>
+        <v>299.4328006905</v>
       </c>
       <c r="C11" t="n">
         <v>22.6390072732588</v>
       </c>
       <c r="D11" t="n">
-        <v>-174.084999126668</v>
+        <v>-174.084996009445</v>
       </c>
     </row>
     <row r="12">
@@ -7371,13 +7371,13 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>284.06740407666</v>
+        <v>284.067403881668</v>
       </c>
       <c r="C12" t="n">
         <v>19.3315654852518</v>
       </c>
       <c r="D12" t="n">
-        <v>-174.084999126668</v>
+        <v>-174.084996009445</v>
       </c>
     </row>
     <row r="13">
@@ -7385,13 +7385,13 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>309.111340898947</v>
+        <v>309.111340688452</v>
       </c>
       <c r="C13" t="n">
         <v>20.2569393385724</v>
       </c>
       <c r="D13" t="n">
-        <v>-174.084999126668</v>
+        <v>-174.084996009445</v>
       </c>
     </row>
     <row r="14">
@@ -7399,13 +7399,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>323.036652534173</v>
+        <v>323.036652600499</v>
       </c>
       <c r="C14" t="n">
         <v>21.2635057619602</v>
       </c>
       <c r="D14" t="n">
-        <v>-278.189249298083</v>
+        <v>-278.189246054065</v>
       </c>
     </row>
     <row r="15">
@@ -7413,13 +7413,13 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>342.687826248879</v>
+        <v>342.687826290645</v>
       </c>
       <c r="C15" t="n">
         <v>21.9922000041835</v>
       </c>
       <c r="D15" t="n">
-        <v>-278.189249298083</v>
+        <v>-278.189246054065</v>
       </c>
     </row>
     <row r="16">
@@ -7427,13 +7427,13 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>345.886644506453</v>
+        <v>345.886644589763</v>
       </c>
       <c r="C16" t="n">
         <v>22.3679119304002</v>
       </c>
       <c r="D16" t="n">
-        <v>-278.189249298083</v>
+        <v>-278.189246054065</v>
       </c>
     </row>
     <row r="17">
@@ -7441,13 +7441,13 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>312.164038731171</v>
+        <v>312.164038539768</v>
       </c>
       <c r="C17" t="n">
         <v>19.54760372866</v>
       </c>
       <c r="D17" t="n">
-        <v>-278.189249298083</v>
+        <v>-278.189246054065</v>
       </c>
     </row>
     <row r="18">
@@ -7455,13 +7455,13 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>315.928054019152</v>
+        <v>315.928053662147</v>
       </c>
       <c r="C18" t="n">
         <v>20.1695374222423</v>
       </c>
       <c r="D18" t="n">
-        <v>-150.139209161164</v>
+        <v>-150.139206087434</v>
       </c>
     </row>
     <row r="19">
@@ -7469,13 +7469,13 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>319.353964169021</v>
+        <v>319.353964364185</v>
       </c>
       <c r="C19" t="n">
         <v>23.1070041934309</v>
       </c>
       <c r="D19" t="n">
-        <v>-150.139209161164</v>
+        <v>-150.139206087434</v>
       </c>
     </row>
     <row r="20">
@@ -7483,13 +7483,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>302.795313537943</v>
+        <v>302.795313671483</v>
       </c>
       <c r="C20" t="n">
         <v>21.9346280696804</v>
       </c>
       <c r="D20" t="n">
-        <v>-150.139209161164</v>
+        <v>-150.139206087434</v>
       </c>
     </row>
     <row r="21">
@@ -7497,13 +7497,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>296.775774968258</v>
+        <v>296.775774996559</v>
       </c>
       <c r="C21" t="n">
         <v>20.8919745070029</v>
       </c>
       <c r="D21" t="n">
-        <v>-150.139209161164</v>
+        <v>-150.139206087434</v>
       </c>
     </row>
     <row r="22">
@@ -7511,13 +7511,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>289.103141220316</v>
+        <v>289.103141539905</v>
       </c>
       <c r="C22" t="n">
         <v>21.0463432330779</v>
       </c>
       <c r="D22" t="n">
-        <v>-245.770844974908</v>
+        <v>-245.770842026513</v>
       </c>
     </row>
     <row r="23">
@@ -7525,13 +7525,13 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>298.435237341677</v>
+        <v>298.435237630015</v>
       </c>
       <c r="C23" t="n">
         <v>20.766927703781</v>
       </c>
       <c r="D23" t="n">
-        <v>-245.770844974908</v>
+        <v>-245.770842026513</v>
       </c>
     </row>
     <row r="24">
@@ -7539,13 +7539,13 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>291.847055444682</v>
+        <v>291.847055432082</v>
       </c>
       <c r="C24" t="n">
         <v>18.2413589421869</v>
       </c>
       <c r="D24" t="n">
-        <v>-245.770844974908</v>
+        <v>-245.770842026513</v>
       </c>
     </row>
     <row r="25">
@@ -7553,13 +7553,13 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>268.690631537651</v>
+        <v>268.690630942322</v>
       </c>
       <c r="C25" t="n">
         <v>13.3796384160073</v>
       </c>
       <c r="D25" t="n">
-        <v>-245.770844974908</v>
+        <v>-245.770842026513</v>
       </c>
     </row>
     <row r="26">
@@ -7567,13 +7567,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>286.308214446608</v>
+        <v>286.30821437986</v>
       </c>
       <c r="C26" t="n">
         <v>14.0182406770477</v>
       </c>
       <c r="D26" t="n">
-        <v>-241.335560903955</v>
+        <v>-241.335556251717</v>
       </c>
     </row>
     <row r="27">
@@ -7581,13 +7581,13 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>291.736371095526</v>
+        <v>291.736371051787</v>
       </c>
       <c r="C27" t="n">
         <v>13.7071095233237</v>
       </c>
       <c r="D27" t="n">
-        <v>-241.335560903955</v>
+        <v>-241.335556251717</v>
       </c>
     </row>
     <row r="28">
@@ -7595,13 +7595,13 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>295.85898902696</v>
+        <v>295.858989025922</v>
       </c>
       <c r="C28" t="n">
         <v>13.8299159840223</v>
       </c>
       <c r="D28" t="n">
-        <v>-241.335560903955</v>
+        <v>-241.335556251717</v>
       </c>
     </row>
     <row r="29">
@@ -7609,13 +7609,13 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>301.36195924588</v>
+        <v>301.361959357404</v>
       </c>
       <c r="C29" t="n">
         <v>14.7597151230636</v>
       </c>
       <c r="D29" t="n">
-        <v>-241.335560903955</v>
+        <v>-241.335556251717</v>
       </c>
     </row>
     <row r="30">
@@ -7623,13 +7623,13 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>314.203715299236</v>
+        <v>314.203715091351</v>
       </c>
       <c r="C30" t="n">
         <v>12.9810429170346</v>
       </c>
       <c r="D30" t="n">
-        <v>-90.8920656050168</v>
+        <v>-90.8920586503998</v>
       </c>
     </row>
     <row r="31">
@@ -7637,13 +7637,13 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>315.026353183591</v>
+        <v>315.02635308007</v>
       </c>
       <c r="C31" t="n">
         <v>13.8683680277628</v>
       </c>
       <c r="D31" t="n">
-        <v>-90.8920656050168</v>
+        <v>-90.8920586503998</v>
       </c>
     </row>
     <row r="32">
@@ -7651,13 +7651,13 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>332.552869515409</v>
+        <v>332.552869863434</v>
       </c>
       <c r="C32" t="n">
         <v>17.0680954411519</v>
       </c>
       <c r="D32" t="n">
-        <v>-90.8920656050168</v>
+        <v>-90.8920586503998</v>
       </c>
     </row>
     <row r="33">
@@ -7665,13 +7665,13 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>303.433621607172</v>
+        <v>303.433621570553</v>
       </c>
       <c r="C33" t="n">
         <v>13.7813182177931</v>
       </c>
       <c r="D33" t="n">
-        <v>-90.8920656050168</v>
+        <v>-90.8920586503998</v>
       </c>
     </row>
     <row r="34">
@@ -7679,13 +7679,13 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>328.624662525499</v>
+        <v>328.6246625348</v>
       </c>
       <c r="C34" t="n">
         <v>15.7211460315555</v>
       </c>
       <c r="D34" t="n">
-        <v>-10.9043203628221</v>
+        <v>-10.9043135943186</v>
       </c>
     </row>
     <row r="35">
@@ -7693,13 +7693,13 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>322.458090450092</v>
+        <v>322.458090483386</v>
       </c>
       <c r="C35" t="n">
         <v>15.2880061963509</v>
       </c>
       <c r="D35" t="n">
-        <v>-10.9043203628221</v>
+        <v>-10.9043135943186</v>
       </c>
     </row>
     <row r="36">
@@ -7707,13 +7707,13 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>316.156005812255</v>
+        <v>316.156005811736</v>
       </c>
       <c r="C36" t="n">
         <v>14.5093569170751</v>
       </c>
       <c r="D36" t="n">
-        <v>-10.9043203628221</v>
+        <v>-10.9043135943186</v>
       </c>
     </row>
     <row r="37">
@@ -7721,13 +7721,13 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>312.398190760935</v>
+        <v>312.398190718858</v>
       </c>
       <c r="C37" t="n">
         <v>13.7574047721106</v>
       </c>
       <c r="D37" t="n">
-        <v>-10.9043203628221</v>
+        <v>-10.9043135943186</v>
       </c>
     </row>
     <row r="38">
@@ -7735,13 +7735,13 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>317.843070612959</v>
+        <v>317.843070579626</v>
       </c>
       <c r="C38" t="n">
         <v>13.8684629626477</v>
       </c>
       <c r="D38" t="n">
-        <v>-7.83852766374252</v>
+        <v>-7.83852110734233</v>
       </c>
     </row>
     <row r="39">
@@ -7749,13 +7749,13 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>323.744960962597</v>
+        <v>323.744960971582</v>
       </c>
       <c r="C39" t="n">
         <v>14.1451731996518</v>
       </c>
       <c r="D39" t="n">
-        <v>-7.83852766374252</v>
+        <v>-7.83852110734233</v>
       </c>
     </row>
     <row r="40">
@@ -7763,13 +7763,13 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>328.281297196447</v>
+        <v>328.281297180948</v>
       </c>
       <c r="C40" t="n">
         <v>14.2458871681251</v>
       </c>
       <c r="D40" t="n">
-        <v>-7.83852766374252</v>
+        <v>-7.83852110734233</v>
       </c>
     </row>
     <row r="41">
@@ -7777,13 +7777,13 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>339.301789335056</v>
+        <v>339.301789374903</v>
       </c>
       <c r="C41" t="n">
         <v>15.2608851765584</v>
       </c>
       <c r="D41" t="n">
-        <v>-7.83852766374252</v>
+        <v>-7.83852110734233</v>
       </c>
     </row>
     <row r="42">
@@ -7791,13 +7791,13 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>360.670442294242</v>
+        <v>360.670442284491</v>
       </c>
       <c r="C42" t="n">
         <v>16.5093813838776</v>
       </c>
       <c r="D42" t="n">
-        <v>34.3347836008113</v>
+        <v>34.3347903933102</v>
       </c>
     </row>
     <row r="43">
@@ -7805,13 +7805,13 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>351.72167442673</v>
+        <v>351.721674227556</v>
       </c>
       <c r="C43" t="n">
         <v>15.1700534476325</v>
       </c>
       <c r="D43" t="n">
-        <v>34.3347836008113</v>
+        <v>34.3347903933102</v>
       </c>
     </row>
     <row r="44">
@@ -7819,13 +7819,13 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>362.542068667197</v>
+        <v>362.542068817434</v>
       </c>
       <c r="C44" t="n">
         <v>16.9821700879659</v>
       </c>
       <c r="D44" t="n">
-        <v>34.3347836008113</v>
+        <v>34.3347903933102</v>
       </c>
     </row>
     <row r="45">
@@ -7833,13 +7833,13 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>340.67991663671</v>
+        <v>340.679916695398</v>
       </c>
       <c r="C45" t="n">
         <v>14.660485780831</v>
       </c>
       <c r="D45" t="n">
-        <v>34.3347836008113</v>
+        <v>34.3347903933102</v>
       </c>
     </row>
     <row r="46">
@@ -7847,13 +7847,13 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>341.19512654259</v>
+        <v>341.195126465823</v>
       </c>
       <c r="C46" t="n">
         <v>13.9855209946961</v>
       </c>
       <c r="D46" t="n">
-        <v>99.0072957470188</v>
+        <v>99.0073017592472</v>
       </c>
     </row>
     <row r="47">
@@ -7861,13 +7861,13 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>324.100236029868</v>
+        <v>324.100235968342</v>
       </c>
       <c r="C47" t="n">
         <v>13.2548173622158</v>
       </c>
       <c r="D47" t="n">
-        <v>99.0072957470188</v>
+        <v>99.0073017592472</v>
       </c>
     </row>
     <row r="48">
@@ -7875,13 +7875,13 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>324.197070063599</v>
+        <v>324.197070186645</v>
       </c>
       <c r="C48" t="n">
         <v>15.4351622089786</v>
       </c>
       <c r="D48" t="n">
-        <v>99.0072957470188</v>
+        <v>99.0073017592472</v>
       </c>
     </row>
     <row r="49">
@@ -7889,13 +7889,13 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>316.769073057839</v>
+        <v>316.769073073085</v>
       </c>
       <c r="C49" t="n">
         <v>17.0935658094356</v>
       </c>
       <c r="D49" t="n">
-        <v>99.0072957470188</v>
+        <v>99.0073017592472</v>
       </c>
     </row>
     <row r="50">
@@ -7903,13 +7903,13 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>314.251940462164</v>
+        <v>314.251941016732</v>
       </c>
       <c r="C50" t="n">
         <v>22.375630978957</v>
       </c>
       <c r="D50" t="n">
-        <v>15.2354701864931</v>
+        <v>15.2354766765689</v>
       </c>
     </row>
     <row r="51">
@@ -7917,13 +7917,13 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>301.011576756511</v>
+        <v>301.011576807114</v>
       </c>
       <c r="C51" t="n">
         <v>21.944785948544</v>
       </c>
       <c r="D51" t="n">
-        <v>15.2354701864931</v>
+        <v>15.2354766765689</v>
       </c>
     </row>
     <row r="52">
@@ -7931,13 +7931,13 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>308.617375769446</v>
+        <v>308.617375569709</v>
       </c>
       <c r="C52" t="n">
         <v>22.6041959806654</v>
       </c>
       <c r="D52" t="n">
-        <v>15.2354701864931</v>
+        <v>15.2354766765689</v>
       </c>
     </row>
     <row r="53">
@@ -7945,13 +7945,13 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>325.881911362545</v>
+        <v>325.881910957113</v>
       </c>
       <c r="C53" t="n">
         <v>22.7999908827289</v>
       </c>
       <c r="D53" t="n">
-        <v>15.2354701864931</v>
+        <v>15.2354766765689</v>
       </c>
     </row>
     <row r="54">
@@ -7959,13 +7959,13 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>313.49123380014</v>
+        <v>313.491233636894</v>
       </c>
       <c r="C54" t="n">
         <v>24.9287895301318</v>
       </c>
       <c r="D54" t="n">
-        <v>-256.934632713396</v>
+        <v>-256.934630252053</v>
       </c>
     </row>
     <row r="55">
@@ -7973,13 +7973,13 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>342.171928234385</v>
+        <v>342.171928303459</v>
       </c>
       <c r="C55" t="n">
         <v>26.2763956711515</v>
       </c>
       <c r="D55" t="n">
-        <v>-256.934632713396</v>
+        <v>-256.934630252053</v>
       </c>
     </row>
     <row r="56">
@@ -7987,13 +7987,13 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>347.10152607871</v>
+        <v>347.101526296976</v>
       </c>
       <c r="C56" t="n">
         <v>25.6964392390321</v>
       </c>
       <c r="D56" t="n">
-        <v>-256.934632713396</v>
+        <v>-256.934630252053</v>
       </c>
     </row>
     <row r="57">
@@ -8001,13 +8001,13 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>306.415875189636</v>
+        <v>306.415875065543</v>
       </c>
       <c r="C57" t="n">
         <v>20.1521132075917</v>
       </c>
       <c r="D57" t="n">
-        <v>-256.934632713396</v>
+        <v>-256.934630252053</v>
       </c>
     </row>
     <row r="58">
@@ -8015,13 +8015,13 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>261.843691659652</v>
+        <v>261.843691228016</v>
       </c>
       <c r="C58" t="n">
         <v>15.247323626023</v>
       </c>
       <c r="D58" t="n">
-        <v>-250.284565731111</v>
+        <v>-250.284564255465</v>
       </c>
     </row>
     <row r="59">
@@ -8029,13 +8029,13 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>256.027099869858</v>
+        <v>256.027099660104</v>
       </c>
       <c r="C59" t="n">
         <v>14.973474992244</v>
       </c>
       <c r="D59" t="n">
-        <v>-250.284565731111</v>
+        <v>-250.284564255465</v>
       </c>
     </row>
     <row r="60">
@@ -8043,13 +8043,13 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>296.583297143916</v>
+        <v>296.583297574635</v>
       </c>
       <c r="C60" t="n">
         <v>20.1965764001429</v>
       </c>
       <c r="D60" t="n">
-        <v>-250.284565731111</v>
+        <v>-250.284564255465</v>
       </c>
     </row>
     <row r="61">
@@ -8057,13 +8057,13 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>315.037238147325</v>
+        <v>315.037238357997</v>
       </c>
       <c r="C61" t="n">
         <v>21.40583148198</v>
       </c>
       <c r="D61" t="n">
-        <v>-250.284565731111</v>
+        <v>-250.284564255465</v>
       </c>
     </row>
     <row r="62">
@@ -8071,13 +8071,13 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>334.309850399312</v>
+        <v>334.309850648598</v>
       </c>
       <c r="C62" t="n">
         <v>21.7281456443213</v>
       </c>
       <c r="D62" t="n">
-        <v>-248.321110121123</v>
+        <v>-248.321105252213</v>
       </c>
     </row>
     <row r="63">
@@ -8085,13 +8085,13 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>351.083413756972</v>
+        <v>351.083413688194</v>
       </c>
       <c r="C63" t="n">
         <v>22.4909049724837</v>
       </c>
       <c r="D63" t="n">
-        <v>-248.321110121123</v>
+        <v>-248.321105252213</v>
       </c>
     </row>
     <row r="64">
@@ -8099,13 +8099,13 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>355.542735745671</v>
+        <v>355.542735509826</v>
       </c>
       <c r="C64" t="n">
         <v>22.2741530256175</v>
       </c>
       <c r="D64" t="n">
-        <v>-248.321110121123</v>
+        <v>-248.321105252213</v>
       </c>
     </row>
     <row r="65">
@@ -8113,13 +8113,13 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>364.135998855462</v>
+        <v>364.135998910799</v>
       </c>
       <c r="C65" t="n">
         <v>23.3624492883955</v>
       </c>
       <c r="D65" t="n">
-        <v>-248.321110121123</v>
+        <v>-248.321105252213</v>
       </c>
     </row>
     <row r="66">
@@ -8127,13 +8127,13 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>411.08256335305</v>
+        <v>411.08256323534</v>
       </c>
       <c r="C66" t="n">
         <v>26.3010438508106</v>
       </c>
       <c r="D66" t="n">
-        <v>-102.568955069101</v>
+        <v>-102.568952625382</v>
       </c>
     </row>
     <row r="67">
@@ -8141,13 +8141,13 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>403.738101038897</v>
+        <v>403.738101181711</v>
       </c>
       <c r="C67" t="n">
         <v>25.8041762528243</v>
       </c>
       <c r="D67" t="n">
-        <v>-102.568955069101</v>
+        <v>-102.568952625382</v>
       </c>
     </row>
     <row r="68">
@@ -8155,13 +8155,13 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>365.569828279525</v>
+        <v>365.569827993108</v>
       </c>
       <c r="C68" t="n">
         <v>20.9236846319188</v>
       </c>
       <c r="D68" t="n">
-        <v>-102.568955069101</v>
+        <v>-102.568952625382</v>
       </c>
     </row>
     <row r="69">
@@ -8169,13 +8169,13 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>385.802625452958</v>
+        <v>385.802625714272</v>
       </c>
       <c r="C69" t="n">
         <v>24.0524000415956</v>
       </c>
       <c r="D69" t="n">
-        <v>-102.568955069101</v>
+        <v>-102.568952625382</v>
       </c>
     </row>
     <row r="70">
@@ -8183,13 +8183,13 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>423.87285950162</v>
+        <v>423.872859536263</v>
       </c>
       <c r="C70" t="n">
         <v>26.4067696723934</v>
       </c>
       <c r="D70" t="n">
-        <v>6.52951355258347</v>
+        <v>6.52951502452152</v>
       </c>
     </row>
     <row r="71">
@@ -8197,13 +8197,13 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>418.291584647536</v>
+        <v>418.291584714728</v>
       </c>
       <c r="C71" t="n">
         <v>26.2388712502691</v>
       </c>
       <c r="D71" t="n">
-        <v>6.52951355258347</v>
+        <v>6.52951502452152</v>
       </c>
     </row>
     <row r="72">
@@ -8211,13 +8211,13 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>387.424212122753</v>
+        <v>387.424211831142</v>
       </c>
       <c r="C72" t="n">
         <v>22.9500627992814</v>
       </c>
       <c r="D72" t="n">
-        <v>6.52951355258347</v>
+        <v>6.52951502452152</v>
       </c>
     </row>
     <row r="73">
@@ -8225,13 +8225,13 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>397.19940227713</v>
+        <v>397.199402466907</v>
       </c>
       <c r="C73" t="n">
         <v>25.6974622201534</v>
       </c>
       <c r="D73" t="n">
-        <v>6.52951355258347</v>
+        <v>6.52951502452152</v>
       </c>
     </row>
     <row r="74">
@@ -8239,13 +8239,13 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>375.828168746066</v>
+        <v>375.828168579019</v>
       </c>
       <c r="C74" t="n">
         <v>23.6361191870476</v>
       </c>
       <c r="D74" t="n">
-        <v>36.8002441990616</v>
+        <v>36.800245104545</v>
       </c>
     </row>
     <row r="75">
@@ -8253,13 +8253,13 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>386.040117642669</v>
+        <v>386.040117756547</v>
       </c>
       <c r="C75" t="n">
         <v>25.3564552861445</v>
       </c>
       <c r="D75" t="n">
-        <v>36.8002441990616</v>
+        <v>36.800245104545</v>
       </c>
     </row>
     <row r="76">
@@ -8267,13 +8267,13 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>392.687156162907</v>
+        <v>392.687156201502</v>
       </c>
       <c r="C76" t="n">
         <v>25.1027329943762</v>
       </c>
       <c r="D76" t="n">
-        <v>36.8002441990616</v>
+        <v>36.800245104545</v>
       </c>
     </row>
     <row r="77">
@@ -8281,13 +8281,13 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>417.582557448357</v>
+        <v>417.582557462932</v>
       </c>
       <c r="C77" t="n">
         <v>25.9046925324318</v>
       </c>
       <c r="D77" t="n">
-        <v>36.8002441990616</v>
+        <v>36.800245104545</v>
       </c>
     </row>
     <row r="78">
@@ -8295,13 +8295,13 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>444.424450295551</v>
+        <v>444.424450398001</v>
       </c>
       <c r="C78" t="n">
         <v>26.8069768911658</v>
       </c>
       <c r="D78" t="n">
-        <v>-8.53938511920455</v>
+        <v>-8.53938403980283</v>
       </c>
     </row>
     <row r="79">
@@ -8309,13 +8309,13 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>461.080767736966</v>
+        <v>461.080767758014</v>
       </c>
       <c r="C79" t="n">
         <v>27.0678469006352</v>
       </c>
       <c r="D79" t="n">
-        <v>-8.53938511920455</v>
+        <v>-8.53938403980283</v>
       </c>
     </row>
     <row r="80">
@@ -8323,13 +8323,13 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>446.246888579598</v>
+        <v>446.246888317147</v>
       </c>
       <c r="C80" t="n">
         <v>25.0370918835188</v>
       </c>
       <c r="D80" t="n">
-        <v>-8.53938511920455</v>
+        <v>-8.53938403980283</v>
       </c>
     </row>
     <row r="81">
@@ -8337,13 +8337,13 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>447.406893387884</v>
+        <v>447.406893526838</v>
       </c>
       <c r="C81" t="n">
         <v>27.3099819670809</v>
       </c>
       <c r="D81" t="n">
-        <v>-8.53938511920455</v>
+        <v>-8.53938403980283</v>
       </c>
     </row>
     <row r="82">
@@ -8351,13 +8351,13 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>476.381891540752</v>
+        <v>476.381891490619</v>
       </c>
       <c r="C82" t="n">
         <v>30.2678629991828</v>
       </c>
       <c r="D82" t="n">
-        <v>173.685710662393</v>
+        <v>173.685710905009</v>
       </c>
     </row>
     <row r="83">
@@ -8365,13 +8365,13 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>458.039044236836</v>
+        <v>458.039044297561</v>
       </c>
       <c r="C83" t="n">
         <v>30.0759732328241</v>
       </c>
       <c r="D83" t="n">
-        <v>173.685710662393</v>
+        <v>173.685710905009</v>
       </c>
     </row>
     <row r="84">
@@ -8379,13 +8379,13 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>440.104989294513</v>
+        <v>440.104989161359</v>
       </c>
       <c r="C84" t="n">
         <v>28.1027332639806</v>
       </c>
       <c r="D84" t="n">
-        <v>173.685710662393</v>
+        <v>173.685710905009</v>
       </c>
     </row>
     <row r="85">
@@ -8393,13 +8393,13 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>462.961525476413</v>
+        <v>462.961525598975</v>
       </c>
       <c r="C85" t="n">
         <v>29.9569464620881</v>
       </c>
       <c r="D85" t="n">
-        <v>173.685710662393</v>
+        <v>173.685710905009</v>
       </c>
     </row>
     <row r="86">
@@ -8407,13 +8407,13 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>489.784070498713</v>
+        <v>489.784070656478</v>
       </c>
       <c r="C86" t="n">
         <v>31.9492837695939</v>
       </c>
       <c r="D86" t="n">
-        <v>124.309952839589</v>
+        <v>124.309951443895</v>
       </c>
     </row>
     <row r="87">
@@ -8421,13 +8421,13 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>496.628948346329</v>
+        <v>496.628948280902</v>
       </c>
       <c r="C87" t="n">
         <v>30.5324798214385</v>
       </c>
       <c r="D87" t="n">
-        <v>124.309952839589</v>
+        <v>124.309951443895</v>
       </c>
     </row>
     <row r="88">
@@ -8435,13 +8435,13 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>490.912202163045</v>
+        <v>490.91220177234</v>
       </c>
       <c r="C88" t="n">
         <v>28.1619781201749</v>
       </c>
       <c r="D88" t="n">
-        <v>124.309952839589</v>
+        <v>124.309951443895</v>
       </c>
     </row>
     <row r="89">
@@ -8449,13 +8449,13 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>532.400451859865</v>
+        <v>532.400452158233</v>
       </c>
       <c r="C89" t="n">
         <v>33.1390240141613</v>
       </c>
       <c r="D89" t="n">
-        <v>124.309952839589</v>
+        <v>124.309951443895</v>
       </c>
     </row>
     <row r="90">
@@ -8463,13 +8463,13 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>564.930924662846</v>
+        <v>564.93092449636</v>
       </c>
       <c r="C90" t="n">
         <v>33.8087363054348</v>
       </c>
       <c r="D90" t="n">
-        <v>257.81909744158</v>
+        <v>257.819095322429</v>
       </c>
     </row>
     <row r="91">
@@ -8477,13 +8477,13 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>569.749617156109</v>
+        <v>569.749617279907</v>
       </c>
       <c r="C91" t="n">
         <v>35.1368582395621</v>
       </c>
       <c r="D91" t="n">
-        <v>257.81909744158</v>
+        <v>257.819095322429</v>
       </c>
     </row>
     <row r="92">
@@ -8491,13 +8491,13 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>535.396912014082</v>
+        <v>535.396911850078</v>
       </c>
       <c r="C92" t="n">
         <v>31.6775239815922</v>
       </c>
       <c r="D92" t="n">
-        <v>257.81909744158</v>
+        <v>257.819095322429</v>
       </c>
     </row>
     <row r="93">
@@ -8505,13 +8505,13 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>528.071237001773</v>
+        <v>528.071237208465</v>
       </c>
       <c r="C93" t="n">
         <v>32.625320599879</v>
       </c>
       <c r="D93" t="n">
-        <v>257.81909744158</v>
+        <v>257.819095322429</v>
       </c>
     </row>
     <row r="94">
@@ -8519,13 +8519,13 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>519.751471080014</v>
+        <v>519.751470655725</v>
       </c>
       <c r="C94" t="n">
-        <v>30.6161933310345</v>
+        <v>30.6161933311176</v>
       </c>
       <c r="D94" t="n">
-        <v>378.09194267838</v>
+        <v>378.091939286187</v>
       </c>
     </row>
     <row r="95">
@@ -8533,13 +8533,13 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>515.660599623099</v>
+        <v>515.660599618959</v>
       </c>
       <c r="C95" t="n">
-        <v>32.0118849853594</v>
+        <v>32.011884985538</v>
       </c>
       <c r="D95" t="n">
-        <v>378.09194267838</v>
+        <v>378.091939286187</v>
       </c>
     </row>
     <row r="96">
@@ -8547,13 +8547,13 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>506.379158787386</v>
+        <v>506.379158940816</v>
       </c>
       <c r="C96" t="n">
-        <v>32.0320057364502</v>
+        <v>32.0320057366789</v>
       </c>
       <c r="D96" t="n">
-        <v>378.09194267838</v>
+        <v>378.091939286187</v>
       </c>
     </row>
     <row r="97">
@@ -8561,13 +8561,13 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>504.031107737758</v>
+        <v>504.031108012757</v>
       </c>
       <c r="C97" t="n">
-        <v>32.3605049154058</v>
+        <v>32.3605049156537</v>
       </c>
       <c r="D97" t="n">
-        <v>378.09194267838</v>
+        <v>378.091939286187</v>
       </c>
     </row>
     <row r="98">
@@ -8575,13 +8575,13 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>526.846696127042</v>
+        <v>526.846695895814</v>
       </c>
       <c r="C98" t="n">
-        <v>35.2134044979178</v>
+        <v>35.2134044981491</v>
       </c>
       <c r="D98" t="n">
-        <v>69.9367303681703</v>
+        <v>69.9367298956742</v>
       </c>
     </row>
     <row r="99">
@@ -8589,13 +8589,13 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>518.590246542292</v>
+        <v>518.59024612749</v>
       </c>
       <c r="C99" t="n">
-        <v>34.1722027802198</v>
+        <v>34.1722027804256</v>
       </c>
       <c r="D99" t="n">
-        <v>69.022473193048</v>
+        <v>69.0224726535581</v>
       </c>
     </row>
     <row r="100">
@@ -8603,13 +8603,13 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>510.670571241531</v>
+        <v>510.670570620556</v>
       </c>
       <c r="C100" t="n">
-        <v>33.2833495200553</v>
+        <v>33.283349520273</v>
       </c>
       <c r="D100" t="n">
-        <v>67.1939588428035</v>
+        <v>67.1939581693258</v>
       </c>
     </row>
     <row r="101">
@@ -8617,13 +8617,13 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>513.370400017538</v>
+        <v>513.370399359764</v>
       </c>
       <c r="C101" t="n">
-        <v>33.9750577063441</v>
+        <v>33.9750577065965</v>
       </c>
       <c r="D101" t="n">
-        <v>64.4511873174367</v>
+        <v>64.4511864429774</v>
       </c>
     </row>
     <row r="102">
@@ -8631,13 +8631,13 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>519.344828515275</v>
+        <v>519.344827852348</v>
       </c>
       <c r="C102" t="n">
-        <v>35.2271616813631</v>
+        <v>35.2271616815998</v>
       </c>
       <c r="D102" t="n">
-        <v>60.7941586169476</v>
+        <v>60.7941574745128</v>
       </c>
     </row>
     <row r="103">
@@ -8645,13 +8645,13 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>519.051351094882</v>
+        <v>519.051350331875</v>
       </c>
       <c r="C103" t="n">
-        <v>35.5655074591262</v>
+        <v>35.565507459343</v>
       </c>
       <c r="D103" t="n">
-        <v>57.5110819811322</v>
+        <v>57.5110806104634</v>
       </c>
     </row>
     <row r="104">
@@ -8659,13 +8659,13 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>509.05376110857</v>
+        <v>509.053760086508</v>
       </c>
       <c r="C104" t="n">
-        <v>34.512825378183</v>
+        <v>34.5128253783955</v>
       </c>
       <c r="D104" t="n">
-        <v>54.6019574099905</v>
+        <v>54.6019558508291</v>
       </c>
     </row>
     <row r="105">
@@ -8673,13 +8673,13 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>512.048736104612</v>
+        <v>512.048735088565</v>
       </c>
       <c r="C105" t="n">
-        <v>35.2215555330435</v>
+        <v>35.2215555332773</v>
       </c>
       <c r="D105" t="n">
-        <v>52.0667849035225</v>
+        <v>52.06678319561</v>
       </c>
     </row>
     <row r="106">
@@ -8687,13 +8687,13 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>510.7688820651</v>
+        <v>510.768880997247</v>
       </c>
       <c r="C106" t="n">
-        <v>35.2933545928841</v>
+        <v>35.2933545931177</v>
       </c>
       <c r="D106" t="n">
-        <v>49.9055644617282</v>
+        <v>49.9055626448061</v>
       </c>
     </row>
     <row r="107">
@@ -8701,13 +8701,13 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>515.475073406357</v>
+        <v>515.475072403904</v>
       </c>
       <c r="C107" t="n">
-        <v>36.1921582505527</v>
+        <v>36.1921582507636</v>
       </c>
       <c r="D107" t="n">
-        <v>47.7826492527057</v>
+        <v>47.7826473347866</v>
       </c>
     </row>
     <row r="108">
@@ -8715,13 +8715,13 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>510.325291633888</v>
+        <v>510.325290518459</v>
       </c>
       <c r="C108" t="n">
-        <v>35.7175997707065</v>
+        <v>35.7175997709202</v>
       </c>
       <c r="D108" t="n">
-        <v>45.6980392764549</v>
+        <v>45.6980372655516</v>
       </c>
     </row>
     <row r="109">
@@ -8729,13 +8729,13 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>511.369582677866</v>
+        <v>511.369581570537</v>
       </c>
       <c r="C109" t="n">
-        <v>36.0989397224926</v>
+        <v>36.0989397226842</v>
       </c>
       <c r="D109" t="n">
-        <v>43.6517345329759</v>
+        <v>43.6517324371011</v>
       </c>
     </row>
     <row r="110">
@@ -8743,13 +8743,13 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>504.789174548806</v>
+        <v>504.789173313078</v>
       </c>
       <c r="C110" t="n">
-        <v>35.4168288626618</v>
+        <v>35.416828862884</v>
       </c>
       <c r="D110" t="n">
-        <v>41.6437350222686</v>
+        <v>41.643732849435</v>
       </c>
     </row>
     <row r="111">
@@ -8757,13 +8757,13 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>513.249164050669</v>
+        <v>513.249162974253</v>
       </c>
       <c r="C111" t="n">
-        <v>36.8125205170584</v>
+        <v>36.8125205173762</v>
       </c>
       <c r="D111" t="n">
-        <v>39.7329320561121</v>
+        <v>39.7329298172795</v>
       </c>
     </row>
     <row r="112">
@@ -8771,13 +8771,13 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>511.886238777226</v>
+        <v>511.886237682593</v>
       </c>
       <c r="C112" t="n">
-        <v>36.8326412681406</v>
+        <v>36.8326412685084</v>
       </c>
       <c r="D112" t="n">
-        <v>37.9193256345065</v>
+        <v>37.9193233406343</v>
       </c>
     </row>
     <row r="113">
@@ -8785,13 +8785,13 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>512.824357893969</v>
+        <v>512.82435683017</v>
       </c>
       <c r="C113" t="n">
-        <v>37.1611404470917</v>
+        <v>37.1611404474786</v>
       </c>
       <c r="D113" t="n">
-        <v>36.2029157574517</v>
+        <v>36.2029134194997</v>
       </c>
     </row>
     <row r="114">
@@ -8799,13 +8799,13 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>532.018253200868</v>
+        <v>532.018252514953</v>
       </c>
       <c r="C114" t="n">
-        <v>40.0140400296571</v>
+        <v>40.0140400300274</v>
       </c>
       <c r="D114" t="n">
-        <v>34.5837024249478</v>
+        <v>34.5837000538756</v>
       </c>
     </row>
     <row r="115">
@@ -8813,13 +8813,13 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>523.230469613934</v>
+        <v>523.230468786716</v>
       </c>
       <c r="C115" t="n">
-        <v>38.9728383119093</v>
+        <v>38.9728383122543</v>
       </c>
       <c r="D115" t="n">
-        <v>33.0303433848535</v>
+        <v>33.0303409872557</v>
       </c>
     </row>
     <row r="116">
@@ -8827,13 +8827,13 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>515.594301539364</v>
+        <v>515.594300596194</v>
       </c>
       <c r="C116" t="n">
-        <v>38.0839850517888</v>
+        <v>38.0839850521456</v>
       </c>
       <c r="D116" t="n">
-        <v>31.542838637169</v>
+        <v>31.5428362196401</v>
       </c>
     </row>
     <row r="117">
@@ -8841,13 +8841,13 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>519.3924787686</v>
+        <v>519.392477926804</v>
       </c>
       <c r="C117" t="n">
-        <v>38.7756932380296</v>
+        <v>38.775693238421</v>
       </c>
       <c r="D117" t="n">
-        <v>30.1211881818941</v>
+        <v>30.1211857510288</v>
       </c>
     </row>
     <row r="118">
@@ -8855,13 +8855,13 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>527.280096947437</v>
+        <v>527.280096286617</v>
       </c>
       <c r="C118" t="n">
-        <v>40.0277972130245</v>
+        <v>40.0277972134002</v>
       </c>
       <c r="D118" t="n">
-        <v>28.7653920190289</v>
+        <v>28.7653895814218</v>
       </c>
     </row>
     <row r="119">
@@ -8869,13 +8869,13 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>528.634798541517</v>
+        <v>528.63479794223</v>
       </c>
       <c r="C119" t="n">
-        <v>40.3661429908133</v>
+        <v>40.3661429911691</v>
       </c>
       <c r="D119" t="n">
-        <v>27.4647864432614</v>
+        <v>27.4647840039946</v>
       </c>
     </row>
     <row r="120">
@@ -8883,13 +8883,13 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>520.020376903037</v>
+        <v>520.020376181797</v>
       </c>
       <c r="C120" t="n">
-        <v>39.3134609099437</v>
+        <v>39.3134609102953</v>
       </c>
       <c r="D120" t="n">
-        <v>26.2193714545915</v>
+        <v>26.219369018747</v>
       </c>
     </row>
     <row r="121">
@@ -8897,13 +8897,13 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>524.133509578846</v>
+        <v>524.133508976209</v>
       </c>
       <c r="C121" t="n">
-        <v>40.0221910647281</v>
+        <v>40.0221910651009</v>
       </c>
       <c r="D121" t="n">
-        <v>25.0291470530193</v>
+        <v>25.0291446256792</v>
       </c>
     </row>
     <row r="122">
@@ -8911,13 +8911,13 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>523.706802552521</v>
+        <v>523.706801986151</v>
       </c>
       <c r="C122" t="n">
-        <v>40.093990124549</v>
+        <v>40.0939901249215</v>
       </c>
       <c r="D122" t="n">
-        <v>23.8941132385447</v>
+        <v>23.8941108247911</v>
       </c>
     </row>
     <row r="123">
@@ -8925,13 +8925,13 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>529.283260199578</v>
+        <v>529.283259781854</v>
       </c>
       <c r="C123" t="n">
-        <v>40.9927937822552</v>
+        <v>40.9927937826051</v>
       </c>
       <c r="D123" t="n">
-        <v>22.8179761709067</v>
+        <v>22.817973773277</v>
       </c>
     </row>
     <row r="124">
@@ -8939,13 +8939,13 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>525.020864024802</v>
+        <v>525.020863572517</v>
       </c>
       <c r="C124" t="n">
-        <v>40.5182353024041</v>
+        <v>40.5182353027568</v>
       </c>
       <c r="D124" t="n">
-        <v>21.8007358501054</v>
+        <v>21.8007334711369</v>
       </c>
     </row>
     <row r="125">
@@ -8953,13 +8953,13 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>526.969659958725</v>
+        <v>526.969659588125</v>
       </c>
       <c r="C125" t="n">
-        <v>40.8995752541926</v>
+        <v>40.8995752545232</v>
       </c>
       <c r="D125" t="n">
-        <v>20.8423922761406</v>
+        <v>20.8423899183709</v>
       </c>
     </row>
     <row r="126">
@@ -8967,13 +8967,13 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>521.310876011989</v>
+        <v>521.310875581744</v>
       </c>
       <c r="C126" t="n">
-        <v>40.2174643943892</v>
+        <v>40.2174643947504</v>
       </c>
       <c r="D126" t="n">
-        <v>19.9429454490125</v>
+        <v>19.9429431149788</v>
       </c>
     </row>
     <row r="127">
@@ -8981,13 +8981,13 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>530.604424023803</v>
+        <v>530.604423818078</v>
       </c>
       <c r="C127" t="n">
-        <v>41.6131560487492</v>
+        <v>41.6131560492058</v>
       </c>
       <c r="D127" t="n">
-        <v>19.0347675672858</v>
+        <v>19.0347652619635</v>
       </c>
     </row>
     <row r="128">
@@ -8995,13 +8995,13 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>529.986991588806</v>
+        <v>529.986991426528</v>
       </c>
       <c r="C128" t="n">
-        <v>41.6332767998515</v>
+        <v>41.6332768003583</v>
       </c>
       <c r="D128" t="n">
-        <v>18.1178586309605</v>
+        <v>18.1178563593247</v>
       </c>
     </row>
     <row r="129">
@@ -9009,13 +9009,13 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>531.582537871801</v>
+        <v>531.582537798476</v>
       </c>
       <c r="C129" t="n">
-        <v>41.9617759787839</v>
+        <v>41.9617759793098</v>
       </c>
       <c r="D129" t="n">
-        <v>17.1922186400367</v>
+        <v>17.1922164070626</v>
       </c>
     </row>
     <row r="130">
@@ -9023,13 +9023,13 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>551.345794672611</v>
+        <v>551.345795031742</v>
       </c>
       <c r="C130" t="n">
-        <v>44.8146755612712</v>
+        <v>44.8146755617805</v>
       </c>
       <c r="D130" t="n">
-        <v>16.2578475945143</v>
+        <v>16.2578454051772</v>
       </c>
     </row>
     <row r="131">
@@ -9037,13 +9037,13 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>543.266826331154</v>
+        <v>543.266826586737</v>
       </c>
       <c r="C131" t="n">
-        <v>43.7734738436028</v>
+        <v>43.7734738440867</v>
       </c>
       <c r="D131" t="n">
-        <v>15.5570693103726</v>
+        <v>15.5570671537632</v>
       </c>
     </row>
     <row r="132">
@@ -9051,13 +9051,13 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>536.47892725185</v>
+        <v>536.478927412421</v>
       </c>
       <c r="C132" t="n">
-        <v>42.8846205834723</v>
+        <v>42.8846205839681</v>
       </c>
       <c r="D132" t="n">
-        <v>15.0898837876114</v>
+        <v>15.0898816528204</v>
       </c>
     </row>
     <row r="133">
@@ -9065,13 +9065,13 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>541.264827226899</v>
+        <v>541.26482749297</v>
       </c>
       <c r="C133" t="n">
-        <v>43.5763287697191</v>
+        <v>43.5763287702496</v>
       </c>
       <c r="D133" t="n">
-        <v>14.8562910262308</v>
+        <v>14.8562889023491</v>
       </c>
     </row>
   </sheetData>
@@ -9098,7 +9098,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>323.547632548277</v>
+        <v>323.547632744127</v>
       </c>
     </row>
     <row r="3">
@@ -9106,7 +9106,7 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>327.498294975882</v>
+        <v>327.498295167857</v>
       </c>
     </row>
     <row r="4">
@@ -9114,7 +9114,7 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>313.845887666642</v>
+        <v>313.845887448242</v>
       </c>
     </row>
     <row r="5">
@@ -9122,7 +9122,7 @@
         <v>34</v>
       </c>
       <c r="B5" t="n">
-        <v>328.942145051602</v>
+        <v>328.942144882177</v>
       </c>
     </row>
     <row r="6">
@@ -9130,7 +9130,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>331.57857151585</v>
+        <v>331.578571696054</v>
       </c>
     </row>
     <row r="7">
@@ -9138,7 +9138,7 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>335.468135029047</v>
+        <v>335.468135139372</v>
       </c>
     </row>
     <row r="8">
@@ -9146,7 +9146,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="n">
-        <v>311.634257917617</v>
+        <v>311.634257608347</v>
       </c>
     </row>
     <row r="9">
@@ -9154,7 +9154,7 @@
         <v>37</v>
       </c>
       <c r="B9" t="n">
-        <v>318.82008032178</v>
+        <v>318.82008034052</v>
       </c>
     </row>
     <row r="10">
@@ -9162,7 +9162,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>293.997524990506</v>
+        <v>293.997525102392</v>
       </c>
     </row>
     <row r="11">
@@ -9170,7 +9170,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>299.432800396899</v>
+        <v>299.4328006905</v>
       </c>
     </row>
     <row r="12">
@@ -9178,7 +9178,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>284.06740407666</v>
+        <v>284.067403881668</v>
       </c>
     </row>
     <row r="13">
@@ -9186,7 +9186,7 @@
         <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>309.111340898947</v>
+        <v>309.111340688452</v>
       </c>
     </row>
     <row r="14">
@@ -9194,7 +9194,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>323.036652534173</v>
+        <v>323.036652600499</v>
       </c>
     </row>
     <row r="15">
@@ -9202,7 +9202,7 @@
         <v>41</v>
       </c>
       <c r="B15" t="n">
-        <v>342.687826248879</v>
+        <v>342.687826290645</v>
       </c>
     </row>
     <row r="16">
@@ -9210,7 +9210,7 @@
         <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>345.886644506453</v>
+        <v>345.886644589763</v>
       </c>
     </row>
     <row r="17">
@@ -9218,7 +9218,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>312.164038731171</v>
+        <v>312.164038539768</v>
       </c>
     </row>
     <row r="18">
@@ -9226,7 +9226,7 @@
         <v>7</v>
       </c>
       <c r="B18" t="n">
-        <v>315.928054019152</v>
+        <v>315.928053662147</v>
       </c>
     </row>
     <row r="19">
@@ -9234,7 +9234,7 @@
         <v>44</v>
       </c>
       <c r="B19" t="n">
-        <v>319.353964169021</v>
+        <v>319.353964364185</v>
       </c>
     </row>
     <row r="20">
@@ -9242,7 +9242,7 @@
         <v>45</v>
       </c>
       <c r="B20" t="n">
-        <v>302.795313537943</v>
+        <v>302.795313671483</v>
       </c>
     </row>
     <row r="21">
@@ -9250,7 +9250,7 @@
         <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>296.775774968258</v>
+        <v>296.775774996559</v>
       </c>
     </row>
     <row r="22">
@@ -9258,7 +9258,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>289.103141220316</v>
+        <v>289.103141539905</v>
       </c>
     </row>
     <row r="23">
@@ -9266,7 +9266,7 @@
         <v>47</v>
       </c>
       <c r="B23" t="n">
-        <v>298.435237341677</v>
+        <v>298.435237630015</v>
       </c>
     </row>
     <row r="24">
@@ -9274,7 +9274,7 @@
         <v>48</v>
       </c>
       <c r="B24" t="n">
-        <v>291.847055444682</v>
+        <v>291.847055432082</v>
       </c>
     </row>
     <row r="25">
@@ -9282,7 +9282,7 @@
         <v>49</v>
       </c>
       <c r="B25" t="n">
-        <v>268.690631537651</v>
+        <v>268.690630942322</v>
       </c>
     </row>
     <row r="26">
@@ -9290,7 +9290,7 @@
         <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>286.308214446608</v>
+        <v>286.30821437986</v>
       </c>
     </row>
     <row r="27">
@@ -9298,7 +9298,7 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>291.736371095526</v>
+        <v>291.736371051787</v>
       </c>
     </row>
     <row r="28">
@@ -9306,7 +9306,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="n">
-        <v>295.85898902696</v>
+        <v>295.858989025922</v>
       </c>
     </row>
     <row r="29">
@@ -9314,7 +9314,7 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>301.36195924588</v>
+        <v>301.361959357404</v>
       </c>
     </row>
     <row r="30">
@@ -9322,7 +9322,7 @@
         <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>314.203715299236</v>
+        <v>314.203715091351</v>
       </c>
     </row>
     <row r="31">
@@ -9330,7 +9330,7 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>315.026353183591</v>
+        <v>315.02635308007</v>
       </c>
     </row>
     <row r="32">
@@ -9338,7 +9338,7 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>332.552869515409</v>
+        <v>332.552869863434</v>
       </c>
     </row>
     <row r="33">
@@ -9346,7 +9346,7 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>303.433621607172</v>
+        <v>303.433621570553</v>
       </c>
     </row>
     <row r="34">
@@ -9354,7 +9354,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>328.624662525499</v>
+        <v>328.6246625348</v>
       </c>
     </row>
     <row r="35">
@@ -9362,7 +9362,7 @@
         <v>56</v>
       </c>
       <c r="B35" t="n">
-        <v>322.458090450092</v>
+        <v>322.458090483386</v>
       </c>
     </row>
     <row r="36">
@@ -9370,7 +9370,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="n">
-        <v>316.156005812255</v>
+        <v>316.156005811736</v>
       </c>
     </row>
     <row r="37">
@@ -9378,7 +9378,7 @@
         <v>58</v>
       </c>
       <c r="B37" t="n">
-        <v>312.398190760935</v>
+        <v>312.398190718858</v>
       </c>
     </row>
     <row r="38">
@@ -9386,7 +9386,7 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>317.843070612959</v>
+        <v>317.843070579626</v>
       </c>
     </row>
     <row r="39">
@@ -9394,7 +9394,7 @@
         <v>59</v>
       </c>
       <c r="B39" t="n">
-        <v>323.744960962597</v>
+        <v>323.744960971582</v>
       </c>
     </row>
     <row r="40">
@@ -9402,7 +9402,7 @@
         <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>328.281297196447</v>
+        <v>328.281297180948</v>
       </c>
     </row>
     <row r="41">
@@ -9410,7 +9410,7 @@
         <v>61</v>
       </c>
       <c r="B41" t="n">
-        <v>339.301789335056</v>
+        <v>339.301789374903</v>
       </c>
     </row>
     <row r="42">
@@ -9418,7 +9418,7 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>360.670442294242</v>
+        <v>360.670442284491</v>
       </c>
     </row>
     <row r="43">
@@ -9426,7 +9426,7 @@
         <v>62</v>
       </c>
       <c r="B43" t="n">
-        <v>351.72167442673</v>
+        <v>351.721674227556</v>
       </c>
     </row>
     <row r="44">
@@ -9434,7 +9434,7 @@
         <v>63</v>
       </c>
       <c r="B44" t="n">
-        <v>362.542068667197</v>
+        <v>362.542068817434</v>
       </c>
     </row>
     <row r="45">
@@ -9442,7 +9442,7 @@
         <v>64</v>
       </c>
       <c r="B45" t="n">
-        <v>340.67991663671</v>
+        <v>340.679916695398</v>
       </c>
     </row>
     <row r="46">
@@ -9450,7 +9450,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>341.19512654259</v>
+        <v>341.195126465823</v>
       </c>
     </row>
     <row r="47">
@@ -9458,7 +9458,7 @@
         <v>65</v>
       </c>
       <c r="B47" t="n">
-        <v>324.100236029868</v>
+        <v>324.100235968342</v>
       </c>
     </row>
     <row r="48">
@@ -9466,7 +9466,7 @@
         <v>66</v>
       </c>
       <c r="B48" t="n">
-        <v>324.197070063599</v>
+        <v>324.197070186645</v>
       </c>
     </row>
     <row r="49">
@@ -9474,7 +9474,7 @@
         <v>67</v>
       </c>
       <c r="B49" t="n">
-        <v>316.769073057839</v>
+        <v>316.769073073085</v>
       </c>
     </row>
     <row r="50">
@@ -9482,7 +9482,7 @@
         <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>314.251940462164</v>
+        <v>314.251941016732</v>
       </c>
     </row>
     <row r="51">
@@ -9490,7 +9490,7 @@
         <v>68</v>
       </c>
       <c r="B51" t="n">
-        <v>301.011576756511</v>
+        <v>301.011576807114</v>
       </c>
     </row>
     <row r="52">
@@ -9498,7 +9498,7 @@
         <v>69</v>
       </c>
       <c r="B52" t="n">
-        <v>308.617375769446</v>
+        <v>308.617375569709</v>
       </c>
     </row>
     <row r="53">
@@ -9506,7 +9506,7 @@
         <v>70</v>
       </c>
       <c r="B53" t="n">
-        <v>325.881911362545</v>
+        <v>325.881910957113</v>
       </c>
     </row>
     <row r="54">
@@ -9514,7 +9514,7 @@
         <v>16</v>
       </c>
       <c r="B54" t="n">
-        <v>313.49123380014</v>
+        <v>313.491233636894</v>
       </c>
     </row>
     <row r="55">
@@ -9522,7 +9522,7 @@
         <v>71</v>
       </c>
       <c r="B55" t="n">
-        <v>342.171928234385</v>
+        <v>342.171928303459</v>
       </c>
     </row>
     <row r="56">
@@ -9530,7 +9530,7 @@
         <v>72</v>
       </c>
       <c r="B56" t="n">
-        <v>347.10152607871</v>
+        <v>347.101526296976</v>
       </c>
     </row>
     <row r="57">
@@ -9538,7 +9538,7 @@
         <v>73</v>
       </c>
       <c r="B57" t="n">
-        <v>306.415875189636</v>
+        <v>306.415875065543</v>
       </c>
     </row>
     <row r="58">
@@ -9546,7 +9546,7 @@
         <v>17</v>
       </c>
       <c r="B58" t="n">
-        <v>261.843691659652</v>
+        <v>261.843691228016</v>
       </c>
     </row>
     <row r="59">
@@ -9554,7 +9554,7 @@
         <v>74</v>
       </c>
       <c r="B59" t="n">
-        <v>256.027099869858</v>
+        <v>256.027099660104</v>
       </c>
     </row>
     <row r="60">
@@ -9562,7 +9562,7 @@
         <v>75</v>
       </c>
       <c r="B60" t="n">
-        <v>296.583297143916</v>
+        <v>296.583297574635</v>
       </c>
     </row>
     <row r="61">
@@ -9570,7 +9570,7 @@
         <v>76</v>
       </c>
       <c r="B61" t="n">
-        <v>315.037238147325</v>
+        <v>315.037238357997</v>
       </c>
     </row>
     <row r="62">
@@ -9578,7 +9578,7 @@
         <v>18</v>
       </c>
       <c r="B62" t="n">
-        <v>334.309850399312</v>
+        <v>334.309850648598</v>
       </c>
     </row>
     <row r="63">
@@ -9586,7 +9586,7 @@
         <v>77</v>
       </c>
       <c r="B63" t="n">
-        <v>351.083413756972</v>
+        <v>351.083413688194</v>
       </c>
     </row>
     <row r="64">
@@ -9594,7 +9594,7 @@
         <v>78</v>
       </c>
       <c r="B64" t="n">
-        <v>355.542735745671</v>
+        <v>355.542735509826</v>
       </c>
     </row>
     <row r="65">
@@ -9602,7 +9602,7 @@
         <v>79</v>
       </c>
       <c r="B65" t="n">
-        <v>364.135998855462</v>
+        <v>364.135998910799</v>
       </c>
     </row>
     <row r="66">
@@ -9610,7 +9610,7 @@
         <v>19</v>
       </c>
       <c r="B66" t="n">
-        <v>411.08256335305</v>
+        <v>411.08256323534</v>
       </c>
     </row>
     <row r="67">
@@ -9618,7 +9618,7 @@
         <v>80</v>
       </c>
       <c r="B67" t="n">
-        <v>403.738101038897</v>
+        <v>403.738101181711</v>
       </c>
     </row>
     <row r="68">
@@ -9626,7 +9626,7 @@
         <v>81</v>
       </c>
       <c r="B68" t="n">
-        <v>365.569828279525</v>
+        <v>365.569827993108</v>
       </c>
     </row>
     <row r="69">
@@ -9634,7 +9634,7 @@
         <v>82</v>
       </c>
       <c r="B69" t="n">
-        <v>385.802625452958</v>
+        <v>385.802625714272</v>
       </c>
     </row>
     <row r="70">
@@ -9642,7 +9642,7 @@
         <v>20</v>
       </c>
       <c r="B70" t="n">
-        <v>423.87285950162</v>
+        <v>423.872859536263</v>
       </c>
     </row>
     <row r="71">
@@ -9650,7 +9650,7 @@
         <v>83</v>
       </c>
       <c r="B71" t="n">
-        <v>418.291584647536</v>
+        <v>418.291584714728</v>
       </c>
     </row>
     <row r="72">
@@ -9658,7 +9658,7 @@
         <v>84</v>
       </c>
       <c r="B72" t="n">
-        <v>387.424212122753</v>
+        <v>387.424211831142</v>
       </c>
     </row>
     <row r="73">
@@ -9666,7 +9666,7 @@
         <v>85</v>
       </c>
       <c r="B73" t="n">
-        <v>397.19940227713</v>
+        <v>397.199402466907</v>
       </c>
     </row>
     <row r="74">
@@ -9674,7 +9674,7 @@
         <v>21</v>
       </c>
       <c r="B74" t="n">
-        <v>375.828168746066</v>
+        <v>375.828168579019</v>
       </c>
     </row>
     <row r="75">
@@ -9682,7 +9682,7 @@
         <v>86</v>
       </c>
       <c r="B75" t="n">
-        <v>386.040117642669</v>
+        <v>386.040117756547</v>
       </c>
     </row>
     <row r="76">
@@ -9690,7 +9690,7 @@
         <v>87</v>
       </c>
       <c r="B76" t="n">
-        <v>392.687156162907</v>
+        <v>392.687156201502</v>
       </c>
     </row>
     <row r="77">
@@ -9698,7 +9698,7 @@
         <v>88</v>
       </c>
       <c r="B77" t="n">
-        <v>417.582557448357</v>
+        <v>417.582557462932</v>
       </c>
     </row>
     <row r="78">
@@ -9706,7 +9706,7 @@
         <v>22</v>
       </c>
       <c r="B78" t="n">
-        <v>444.424450295551</v>
+        <v>444.424450398001</v>
       </c>
     </row>
     <row r="79">
@@ -9714,7 +9714,7 @@
         <v>89</v>
       </c>
       <c r="B79" t="n">
-        <v>461.080767736966</v>
+        <v>461.080767758014</v>
       </c>
     </row>
     <row r="80">
@@ -9722,7 +9722,7 @@
         <v>90</v>
       </c>
       <c r="B80" t="n">
-        <v>446.246888579598</v>
+        <v>446.246888317147</v>
       </c>
     </row>
     <row r="81">
@@ -9730,7 +9730,7 @@
         <v>91</v>
       </c>
       <c r="B81" t="n">
-        <v>447.406893387884</v>
+        <v>447.406893526838</v>
       </c>
     </row>
     <row r="82">
@@ -9738,7 +9738,7 @@
         <v>23</v>
       </c>
       <c r="B82" t="n">
-        <v>476.381891540752</v>
+        <v>476.381891490619</v>
       </c>
     </row>
     <row r="83">
@@ -9746,7 +9746,7 @@
         <v>92</v>
       </c>
       <c r="B83" t="n">
-        <v>458.039044236836</v>
+        <v>458.039044297561</v>
       </c>
     </row>
     <row r="84">
@@ -9754,7 +9754,7 @@
         <v>93</v>
       </c>
       <c r="B84" t="n">
-        <v>440.104989294513</v>
+        <v>440.104989161359</v>
       </c>
     </row>
     <row r="85">
@@ -9762,7 +9762,7 @@
         <v>94</v>
       </c>
       <c r="B85" t="n">
-        <v>462.961525476413</v>
+        <v>462.961525598975</v>
       </c>
     </row>
     <row r="86">
@@ -9770,7 +9770,7 @@
         <v>24</v>
       </c>
       <c r="B86" t="n">
-        <v>489.784070498713</v>
+        <v>489.784070656478</v>
       </c>
     </row>
     <row r="87">
@@ -9778,7 +9778,7 @@
         <v>95</v>
       </c>
       <c r="B87" t="n">
-        <v>496.628948346329</v>
+        <v>496.628948280902</v>
       </c>
     </row>
     <row r="88">
@@ -9786,7 +9786,7 @@
         <v>96</v>
       </c>
       <c r="B88" t="n">
-        <v>490.912202163045</v>
+        <v>490.91220177234</v>
       </c>
     </row>
     <row r="89">
@@ -9794,7 +9794,7 @@
         <v>97</v>
       </c>
       <c r="B89" t="n">
-        <v>532.400451859865</v>
+        <v>532.400452158233</v>
       </c>
     </row>
     <row r="90">
@@ -9802,7 +9802,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="n">
-        <v>564.930924662846</v>
+        <v>564.93092449636</v>
       </c>
     </row>
     <row r="91">
@@ -9810,7 +9810,7 @@
         <v>98</v>
       </c>
       <c r="B91" t="n">
-        <v>569.749617156109</v>
+        <v>569.749617279907</v>
       </c>
     </row>
     <row r="92">
@@ -9818,7 +9818,7 @@
         <v>99</v>
       </c>
       <c r="B92" t="n">
-        <v>535.396912014082</v>
+        <v>535.396911850078</v>
       </c>
     </row>
     <row r="93">
@@ -9826,7 +9826,7 @@
         <v>100</v>
       </c>
       <c r="B93" t="n">
-        <v>528.071237001773</v>
+        <v>528.071237208465</v>
       </c>
     </row>
     <row r="94">
@@ -9834,7 +9834,7 @@
         <v>26</v>
       </c>
       <c r="B94" t="n">
-        <v>519.751471080014</v>
+        <v>519.751470655725</v>
       </c>
     </row>
     <row r="95">
@@ -9842,7 +9842,7 @@
         <v>101</v>
       </c>
       <c r="B95" t="n">
-        <v>515.660599623099</v>
+        <v>515.660599618959</v>
       </c>
     </row>
     <row r="96">
@@ -9850,7 +9850,7 @@
         <v>102</v>
       </c>
       <c r="B96" t="n">
-        <v>506.379158787386</v>
+        <v>506.379158940816</v>
       </c>
     </row>
     <row r="97">
@@ -9858,7 +9858,7 @@
         <v>103</v>
       </c>
       <c r="B97" t="n">
-        <v>504.031107737758</v>
+        <v>504.031108012757</v>
       </c>
     </row>
     <row r="98">
@@ -9866,7 +9866,7 @@
         <v>104</v>
       </c>
       <c r="B98" t="n">
-        <v>526.846696127042</v>
+        <v>526.846695895814</v>
       </c>
     </row>
     <row r="99">
@@ -9874,7 +9874,7 @@
         <v>105</v>
       </c>
       <c r="B99" t="n">
-        <v>518.590246542292</v>
+        <v>518.59024612749</v>
       </c>
     </row>
     <row r="100">
@@ -9882,7 +9882,7 @@
         <v>106</v>
       </c>
       <c r="B100" t="n">
-        <v>510.670571241531</v>
+        <v>510.670570620556</v>
       </c>
     </row>
     <row r="101">
@@ -9890,7 +9890,7 @@
         <v>107</v>
       </c>
       <c r="B101" t="n">
-        <v>513.370400017538</v>
+        <v>513.370399359764</v>
       </c>
     </row>
     <row r="102">
@@ -9898,7 +9898,7 @@
         <v>108</v>
       </c>
       <c r="B102" t="n">
-        <v>519.344828515275</v>
+        <v>519.344827852348</v>
       </c>
     </row>
     <row r="103">
@@ -9906,7 +9906,7 @@
         <v>109</v>
       </c>
       <c r="B103" t="n">
-        <v>519.051351094882</v>
+        <v>519.051350331875</v>
       </c>
     </row>
     <row r="104">
@@ -9914,7 +9914,7 @@
         <v>110</v>
       </c>
       <c r="B104" t="n">
-        <v>509.05376110857</v>
+        <v>509.053760086508</v>
       </c>
     </row>
     <row r="105">
@@ -9922,7 +9922,7 @@
         <v>111</v>
       </c>
       <c r="B105" t="n">
-        <v>512.048736104612</v>
+        <v>512.048735088565</v>
       </c>
     </row>
     <row r="106">
@@ -9930,7 +9930,7 @@
         <v>112</v>
       </c>
       <c r="B106" t="n">
-        <v>510.7688820651</v>
+        <v>510.768880997247</v>
       </c>
     </row>
     <row r="107">
@@ -9938,7 +9938,7 @@
         <v>113</v>
       </c>
       <c r="B107" t="n">
-        <v>515.475073406357</v>
+        <v>515.475072403904</v>
       </c>
     </row>
     <row r="108">
@@ -9946,7 +9946,7 @@
         <v>114</v>
       </c>
       <c r="B108" t="n">
-        <v>510.325291633888</v>
+        <v>510.325290518459</v>
       </c>
     </row>
     <row r="109">
@@ -9954,7 +9954,7 @@
         <v>115</v>
       </c>
       <c r="B109" t="n">
-        <v>511.369582677866</v>
+        <v>511.369581570537</v>
       </c>
     </row>
     <row r="110">
@@ -9962,7 +9962,7 @@
         <v>116</v>
       </c>
       <c r="B110" t="n">
-        <v>504.789174548806</v>
+        <v>504.789173313078</v>
       </c>
     </row>
     <row r="111">
@@ -9970,7 +9970,7 @@
         <v>117</v>
       </c>
       <c r="B111" t="n">
-        <v>513.249164050669</v>
+        <v>513.249162974253</v>
       </c>
     </row>
     <row r="112">
@@ -9978,7 +9978,7 @@
         <v>118</v>
       </c>
       <c r="B112" t="n">
-        <v>511.886238777226</v>
+        <v>511.886237682593</v>
       </c>
     </row>
     <row r="113">
@@ -9986,7 +9986,7 @@
         <v>119</v>
       </c>
       <c r="B113" t="n">
-        <v>512.824357893969</v>
+        <v>512.82435683017</v>
       </c>
     </row>
     <row r="114">
@@ -9994,7 +9994,7 @@
         <v>120</v>
       </c>
       <c r="B114" t="n">
-        <v>532.018253200868</v>
+        <v>532.018252514953</v>
       </c>
     </row>
     <row r="115">
@@ -10002,7 +10002,7 @@
         <v>121</v>
       </c>
       <c r="B115" t="n">
-        <v>523.230469613934</v>
+        <v>523.230468786716</v>
       </c>
     </row>
     <row r="116">
@@ -10010,7 +10010,7 @@
         <v>122</v>
       </c>
       <c r="B116" t="n">
-        <v>515.594301539364</v>
+        <v>515.594300596194</v>
       </c>
     </row>
     <row r="117">
@@ -10018,7 +10018,7 @@
         <v>123</v>
       </c>
       <c r="B117" t="n">
-        <v>519.3924787686</v>
+        <v>519.392477926804</v>
       </c>
     </row>
     <row r="118">
@@ -10026,7 +10026,7 @@
         <v>124</v>
       </c>
       <c r="B118" t="n">
-        <v>527.280096947437</v>
+        <v>527.280096286617</v>
       </c>
     </row>
     <row r="119">
@@ -10034,7 +10034,7 @@
         <v>125</v>
       </c>
       <c r="B119" t="n">
-        <v>528.634798541517</v>
+        <v>528.63479794223</v>
       </c>
     </row>
     <row r="120">
@@ -10042,7 +10042,7 @@
         <v>126</v>
       </c>
       <c r="B120" t="n">
-        <v>520.020376903037</v>
+        <v>520.020376181797</v>
       </c>
     </row>
     <row r="121">
@@ -10050,7 +10050,7 @@
         <v>127</v>
       </c>
       <c r="B121" t="n">
-        <v>524.133509578846</v>
+        <v>524.133508976209</v>
       </c>
     </row>
     <row r="122">
@@ -10058,7 +10058,7 @@
         <v>128</v>
       </c>
       <c r="B122" t="n">
-        <v>523.706802552521</v>
+        <v>523.706801986151</v>
       </c>
     </row>
     <row r="123">
@@ -10066,7 +10066,7 @@
         <v>129</v>
       </c>
       <c r="B123" t="n">
-        <v>529.283260199578</v>
+        <v>529.283259781854</v>
       </c>
     </row>
     <row r="124">
@@ -10074,7 +10074,7 @@
         <v>130</v>
       </c>
       <c r="B124" t="n">
-        <v>525.020864024802</v>
+        <v>525.020863572517</v>
       </c>
     </row>
     <row r="125">
@@ -10082,7 +10082,7 @@
         <v>131</v>
       </c>
       <c r="B125" t="n">
-        <v>526.969659958725</v>
+        <v>526.969659588125</v>
       </c>
     </row>
     <row r="126">
@@ -10090,7 +10090,7 @@
         <v>132</v>
       </c>
       <c r="B126" t="n">
-        <v>521.310876011989</v>
+        <v>521.310875581744</v>
       </c>
     </row>
     <row r="127">
@@ -10098,7 +10098,7 @@
         <v>133</v>
       </c>
       <c r="B127" t="n">
-        <v>530.604424023803</v>
+        <v>530.604423818078</v>
       </c>
     </row>
     <row r="128">
@@ -10106,7 +10106,7 @@
         <v>134</v>
       </c>
       <c r="B128" t="n">
-        <v>529.986991588806</v>
+        <v>529.986991426528</v>
       </c>
     </row>
     <row r="129">
@@ -10114,7 +10114,7 @@
         <v>135</v>
       </c>
       <c r="B129" t="n">
-        <v>531.582537871801</v>
+        <v>531.582537798476</v>
       </c>
     </row>
     <row r="130">
@@ -10122,7 +10122,7 @@
         <v>136</v>
       </c>
       <c r="B130" t="n">
-        <v>551.345794672611</v>
+        <v>551.345795031742</v>
       </c>
     </row>
     <row r="131">
@@ -10130,7 +10130,7 @@
         <v>137</v>
       </c>
       <c r="B131" t="n">
-        <v>543.266826331154</v>
+        <v>543.266826586737</v>
       </c>
     </row>
     <row r="132">
@@ -10138,7 +10138,7 @@
         <v>138</v>
       </c>
       <c r="B132" t="n">
-        <v>536.47892725185</v>
+        <v>536.478927412421</v>
       </c>
     </row>
     <row r="133">
@@ -10146,7 +10146,7 @@
         <v>139</v>
       </c>
       <c r="B133" t="n">
-        <v>541.264827226899</v>
+        <v>541.26482749297</v>
       </c>
     </row>
   </sheetData>
